--- a/data/Analyse factoren.xlsx
+++ b/data/Analyse factoren.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icthva.sharepoint.com/sites/FT_O_URAN_Urban_Analytics_Team-KIACECBM/Gedeelde documenten/KIA CE CBM/KIA CE CMS_Project/WP1_Datacollectie - Vormen database, meeteenheden en toekomstscenario’s/data prototype/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\GitHub\FLIM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{5A67BABA-8E40-41CC-BF25-64C07F2391C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B1F910E-2E64-4659-9D99-40C927B1DA43}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553152A8-9C03-4D33-B107-1021E8ACA010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3211,7 +3211,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="371">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4030,237 +4030,240 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4268,7 +4271,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Standaard 2" xfId="1" xr:uid="{E775D1F7-5347-4C29-BD9F-B3957D0479EC}"/>
   </cellStyles>
-  <dxfs count="132">
+  <dxfs count="102">
     <dxf>
       <fill>
         <patternFill>
@@ -4392,13 +4395,18 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FFCCCCCC"/>
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4412,16 +4420,19 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFCCCCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4438,6 +4449,22 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFCCCCCC"/>
           <bgColor rgb="FFCCCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4472,45 +4499,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFB6D7A8"/>
           <bgColor rgb="FFB6D7A8"/>
@@ -4530,6 +4518,30 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFCE5CD"/>
           <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4584,8 +4596,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4600,52 +4612,16 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.14996795556505021"/>
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4692,22 +4668,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFB6D7A8"/>
           <bgColor rgb="FFB6D7A8"/>
         </patternFill>
@@ -4724,135 +4684,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFF4CCCC"/>
           <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FFCCCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE8B2"/>
-          <bgColor rgb="FFFCE8B2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FFCCCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FFCCCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4891,160 +4724,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFCCCCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5081,6 +4762,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF4CCCC"/>
           <bgColor rgb="FFF4CCCC"/>
         </patternFill>
@@ -5091,6 +4780,14 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFB6D7A8"/>
           <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5145,8 +4842,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5169,8 +4866,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5225,6 +4922,78 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFCE5CD"/>
           <bgColor rgb="FFFCE5CD"/>
         </patternFill>
@@ -5249,14 +5018,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFF4CCCC"/>
           <bgColor rgb="FFF4CCCC"/>
         </patternFill>
@@ -5275,6 +5036,21 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFCE5CD"/>
           <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB6D7A8"/>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5307,13 +5083,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFB6D7A8"/>
           <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6596,7 +6365,7 @@
       </c>
     </row>
     <row r="3" spans="1:26" ht="26.4">
-      <c r="A3" s="313" t="s">
+      <c r="A3" s="327" t="s">
         <v>89</v>
       </c>
       <c r="B3" s="27" t="s">
@@ -6652,8 +6421,8 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="13.2">
-      <c r="A4" s="313"/>
-      <c r="B4" s="321" t="s">
+      <c r="A4" s="327"/>
+      <c r="B4" s="305" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="98" t="s">
@@ -6668,7 +6437,7 @@
       <c r="F4" s="234" t="s">
         <v>475</v>
       </c>
-      <c r="G4" s="195" t="s">
+      <c r="G4" s="370" t="s">
         <v>494</v>
       </c>
       <c r="H4" s="241">
@@ -6705,8 +6474,8 @@
       </c>
     </row>
     <row r="5" spans="1:26" ht="13.2">
-      <c r="A5" s="313"/>
-      <c r="B5" s="321"/>
+      <c r="A5" s="327"/>
+      <c r="B5" s="305"/>
       <c r="C5" s="98" t="s">
         <v>498</v>
       </c>
@@ -6756,8 +6525,8 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="13.2">
-      <c r="A6" s="313"/>
-      <c r="B6" s="321"/>
+      <c r="A6" s="327"/>
+      <c r="B6" s="305"/>
       <c r="C6" s="98" t="s">
         <v>499</v>
       </c>
@@ -6807,8 +6576,8 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="13.2">
-      <c r="A7" s="313"/>
-      <c r="B7" s="321"/>
+      <c r="A7" s="327"/>
+      <c r="B7" s="305"/>
       <c r="C7" s="98" t="s">
         <v>500</v>
       </c>
@@ -6858,8 +6627,8 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="26.4">
-      <c r="A8" s="313"/>
-      <c r="B8" s="321" t="s">
+      <c r="A8" s="327"/>
+      <c r="B8" s="305" t="s">
         <v>103</v>
       </c>
       <c r="C8" s="114" t="s">
@@ -6906,8 +6675,8 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="13.2">
-      <c r="A9" s="313"/>
-      <c r="B9" s="321"/>
+      <c r="A9" s="327"/>
+      <c r="B9" s="305"/>
       <c r="C9" s="98" t="s">
         <v>106</v>
       </c>
@@ -6944,8 +6713,8 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="13.2">
-      <c r="A10" s="313"/>
-      <c r="B10" s="321"/>
+      <c r="A10" s="327"/>
+      <c r="B10" s="305"/>
       <c r="C10" s="98" t="s">
         <v>528</v>
       </c>
@@ -6984,8 +6753,8 @@
       <c r="Z10" s="25"/>
     </row>
     <row r="11" spans="1:26" ht="13.2">
-      <c r="A11" s="313"/>
-      <c r="B11" s="321"/>
+      <c r="A11" s="327"/>
+      <c r="B11" s="305"/>
       <c r="C11" s="98" t="s">
         <v>107</v>
       </c>
@@ -7032,8 +6801,8 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="39.6">
-      <c r="A12" s="313"/>
-      <c r="B12" s="321"/>
+      <c r="A12" s="327"/>
+      <c r="B12" s="305"/>
       <c r="C12" s="98" t="s">
         <v>109</v>
       </c>
@@ -7083,8 +6852,8 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="39.6">
-      <c r="A13" s="313"/>
-      <c r="B13" s="321"/>
+      <c r="A13" s="327"/>
+      <c r="B13" s="305"/>
       <c r="C13" s="98" t="s">
         <v>109</v>
       </c>
@@ -7123,8 +6892,8 @@
       <c r="Z13" s="25"/>
     </row>
     <row r="14" spans="1:26" ht="13.2">
-      <c r="A14" s="313"/>
-      <c r="B14" s="321"/>
+      <c r="A14" s="327"/>
+      <c r="B14" s="305"/>
       <c r="C14" s="98" t="s">
         <v>110</v>
       </c>
@@ -7174,8 +6943,8 @@
       </c>
     </row>
     <row r="15" spans="1:26" ht="13.2">
-      <c r="A15" s="313"/>
-      <c r="B15" s="321"/>
+      <c r="A15" s="327"/>
+      <c r="B15" s="305"/>
       <c r="C15" s="98" t="s">
         <v>521</v>
       </c>
@@ -7214,8 +6983,8 @@
       <c r="Z15" s="25"/>
     </row>
     <row r="16" spans="1:26" ht="13.2">
-      <c r="A16" s="313"/>
-      <c r="B16" s="321"/>
+      <c r="A16" s="327"/>
+      <c r="B16" s="305"/>
       <c r="C16" s="114" t="s">
         <v>111</v>
       </c>
@@ -7260,8 +7029,8 @@
       </c>
     </row>
     <row r="17" spans="1:26" ht="13.2">
-      <c r="A17" s="313"/>
-      <c r="B17" s="321" t="s">
+      <c r="A17" s="327"/>
+      <c r="B17" s="305" t="s">
         <v>112</v>
       </c>
       <c r="C17" s="98" t="s">
@@ -7332,12 +7101,12 @@
       </c>
     </row>
     <row r="18" spans="1:26" ht="26.4">
-      <c r="A18" s="313"/>
-      <c r="B18" s="321"/>
-      <c r="C18" s="322" t="s">
+      <c r="A18" s="327"/>
+      <c r="B18" s="305"/>
+      <c r="C18" s="296" t="s">
         <v>116</v>
       </c>
-      <c r="D18" s="326" t="s">
+      <c r="D18" s="330" t="s">
         <v>17</v>
       </c>
       <c r="E18" s="57" t="s">
@@ -7385,10 +7154,10 @@
       </c>
     </row>
     <row r="19" spans="1:26" ht="13.2">
-      <c r="A19" s="313"/>
-      <c r="B19" s="321"/>
-      <c r="C19" s="291"/>
-      <c r="D19" s="327"/>
+      <c r="A19" s="327"/>
+      <c r="B19" s="305"/>
+      <c r="C19" s="297"/>
+      <c r="D19" s="331"/>
       <c r="E19" s="104" t="s">
         <v>17</v>
       </c>
@@ -7443,8 +7212,8 @@
       <c r="Z19" s="25"/>
     </row>
     <row r="20" spans="1:26" ht="13.2">
-      <c r="A20" s="313"/>
-      <c r="B20" s="321"/>
+      <c r="A20" s="327"/>
+      <c r="B20" s="305"/>
       <c r="C20" s="98" t="s">
         <v>120</v>
       </c>
@@ -7513,11 +7282,11 @@
       </c>
     </row>
     <row r="21" spans="1:26" ht="16.95" customHeight="1">
-      <c r="A21" s="313"/>
-      <c r="B21" s="323" t="s">
+      <c r="A21" s="327"/>
+      <c r="B21" s="300" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="322" t="s">
+      <c r="C21" s="296" t="s">
         <v>86</v>
       </c>
       <c r="D21" s="57" t="s">
@@ -7587,9 +7356,9 @@
       </c>
     </row>
     <row r="22" spans="1:26" ht="13.2">
-      <c r="A22" s="313"/>
-      <c r="B22" s="324"/>
-      <c r="C22" s="291"/>
+      <c r="A22" s="327"/>
+      <c r="B22" s="301"/>
+      <c r="C22" s="297"/>
       <c r="D22" s="57" t="s">
         <v>17</v>
       </c>
@@ -7645,8 +7414,8 @@
       <c r="Z22" s="25"/>
     </row>
     <row r="23" spans="1:26" ht="13.2">
-      <c r="A23" s="313"/>
-      <c r="B23" s="324"/>
+      <c r="A23" s="327"/>
+      <c r="B23" s="301"/>
       <c r="C23" s="98" t="s">
         <v>123</v>
       </c>
@@ -7715,8 +7484,8 @@
       </c>
     </row>
     <row r="24" spans="1:26" ht="13.2">
-      <c r="A24" s="313"/>
-      <c r="B24" s="324"/>
+      <c r="A24" s="327"/>
+      <c r="B24" s="301"/>
       <c r="C24" s="183" t="s">
         <v>126</v>
       </c>
@@ -7779,8 +7548,8 @@
       </c>
     </row>
     <row r="25" spans="1:26" ht="13.2">
-      <c r="A25" s="313"/>
-      <c r="B25" s="325"/>
+      <c r="A25" s="327"/>
+      <c r="B25" s="329"/>
       <c r="C25" s="60" t="s">
         <v>474</v>
       </c>
@@ -7811,8 +7580,8 @@
       <c r="Z25" s="25"/>
     </row>
     <row r="26" spans="1:26" ht="14.55" customHeight="1">
-      <c r="A26" s="313"/>
-      <c r="B26" s="321" t="s">
+      <c r="A26" s="327"/>
+      <c r="B26" s="305" t="s">
         <v>128</v>
       </c>
       <c r="C26" s="21" t="s">
@@ -7883,8 +7652,8 @@
       </c>
     </row>
     <row r="27" spans="1:26" ht="13.2">
-      <c r="A27" s="313"/>
-      <c r="B27" s="321"/>
+      <c r="A27" s="327"/>
+      <c r="B27" s="305"/>
       <c r="C27" s="98" t="s">
         <v>129</v>
       </c>
@@ -7953,8 +7722,8 @@
       </c>
     </row>
     <row r="28" spans="1:26" ht="13.2">
-      <c r="A28" s="313"/>
-      <c r="B28" s="321"/>
+      <c r="A28" s="327"/>
+      <c r="B28" s="305"/>
       <c r="C28" s="98" t="s">
         <v>132</v>
       </c>
@@ -8023,8 +7792,8 @@
       </c>
     </row>
     <row r="29" spans="1:26" ht="16.05" customHeight="1">
-      <c r="A29" s="313"/>
-      <c r="B29" s="321"/>
+      <c r="A29" s="327"/>
+      <c r="B29" s="305"/>
       <c r="C29" s="98" t="s">
         <v>133</v>
       </c>
@@ -8095,8 +7864,8 @@
       </c>
     </row>
     <row r="30" spans="1:26" ht="13.2">
-      <c r="A30" s="313"/>
-      <c r="B30" s="322" t="s">
+      <c r="A30" s="327"/>
+      <c r="B30" s="296" t="s">
         <v>134</v>
       </c>
       <c r="C30" s="98" t="s">
@@ -8163,8 +7932,8 @@
       </c>
     </row>
     <row r="31" spans="1:26" ht="13.2">
-      <c r="A31" s="313"/>
-      <c r="B31" s="290"/>
+      <c r="A31" s="327"/>
+      <c r="B31" s="328"/>
       <c r="C31" s="98" t="s">
         <v>135</v>
       </c>
@@ -8227,7 +7996,7 @@
       <c r="V31" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="W31" s="320" t="s">
+      <c r="W31" s="326" t="s">
         <v>139</v>
       </c>
       <c r="X31" s="25"/>
@@ -8237,12 +8006,12 @@
       </c>
     </row>
     <row r="32" spans="1:26" ht="13.2">
-      <c r="A32" s="313"/>
-      <c r="B32" s="290"/>
-      <c r="C32" s="322" t="s">
+      <c r="A32" s="327"/>
+      <c r="B32" s="328"/>
+      <c r="C32" s="296" t="s">
         <v>140</v>
       </c>
-      <c r="D32" s="328" t="s">
+      <c r="D32" s="307" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="104" t="s">
@@ -8301,7 +8070,7 @@
       <c r="V32" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="W32" s="320"/>
+      <c r="W32" s="326"/>
       <c r="X32" s="25"/>
       <c r="Y32" s="25"/>
       <c r="Z32" s="25" t="s">
@@ -8309,10 +8078,10 @@
       </c>
     </row>
     <row r="33" spans="1:26" ht="13.2">
-      <c r="A33" s="313"/>
-      <c r="B33" s="290"/>
-      <c r="C33" s="291"/>
-      <c r="D33" s="329"/>
+      <c r="A33" s="327"/>
+      <c r="B33" s="328"/>
+      <c r="C33" s="297"/>
+      <c r="D33" s="309"/>
       <c r="E33" s="104" t="s">
         <v>17</v>
       </c>
@@ -8358,14 +8127,14 @@
       <c r="T33" s="26"/>
       <c r="U33" s="25"/>
       <c r="V33" s="25"/>
-      <c r="W33" s="320"/>
+      <c r="W33" s="326"/>
       <c r="X33" s="25"/>
       <c r="Y33" s="25"/>
       <c r="Z33" s="25"/>
     </row>
     <row r="34" spans="1:26" ht="13.2">
-      <c r="A34" s="313"/>
-      <c r="B34" s="290"/>
+      <c r="A34" s="327"/>
+      <c r="B34" s="328"/>
       <c r="C34" s="98" t="s">
         <v>142</v>
       </c>
@@ -8404,7 +8173,7 @@
       <c r="V34" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="W34" s="320"/>
+      <c r="W34" s="326"/>
       <c r="X34" s="25"/>
       <c r="Y34" s="25"/>
       <c r="Z34" s="25" t="s">
@@ -8412,9 +8181,9 @@
       </c>
     </row>
     <row r="35" spans="1:26" ht="13.2">
-      <c r="A35" s="313"/>
-      <c r="B35" s="290"/>
-      <c r="C35" s="322" t="s">
+      <c r="A35" s="327"/>
+      <c r="B35" s="328"/>
+      <c r="C35" s="296" t="s">
         <v>143</v>
       </c>
       <c r="D35" s="57" t="s">
@@ -8476,7 +8245,7 @@
       <c r="V35" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="W35" s="320"/>
+      <c r="W35" s="326"/>
       <c r="X35" s="25"/>
       <c r="Y35" s="25"/>
       <c r="Z35" s="25" t="s">
@@ -8484,9 +8253,9 @@
       </c>
     </row>
     <row r="36" spans="1:26" ht="13.2">
-      <c r="A36" s="313"/>
-      <c r="B36" s="290"/>
-      <c r="C36" s="291"/>
+      <c r="A36" s="327"/>
+      <c r="B36" s="328"/>
+      <c r="C36" s="297"/>
       <c r="D36" s="57" t="s">
         <v>23</v>
       </c>
@@ -8533,18 +8302,18 @@
       <c r="T36" s="26"/>
       <c r="U36" s="25"/>
       <c r="V36" s="25"/>
-      <c r="W36" s="320"/>
+      <c r="W36" s="326"/>
       <c r="X36" s="25"/>
       <c r="Y36" s="25"/>
       <c r="Z36" s="25"/>
     </row>
     <row r="37" spans="1:26" ht="13.2">
-      <c r="A37" s="313"/>
-      <c r="B37" s="290"/>
-      <c r="C37" s="322" t="s">
+      <c r="A37" s="327"/>
+      <c r="B37" s="328"/>
+      <c r="C37" s="296" t="s">
         <v>144</v>
       </c>
-      <c r="D37" s="328" t="s">
+      <c r="D37" s="307" t="s">
         <v>17</v>
       </c>
       <c r="E37" s="104" t="s">
@@ -8601,7 +8370,7 @@
       <c r="V37" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="W37" s="320"/>
+      <c r="W37" s="326"/>
       <c r="X37" s="25"/>
       <c r="Y37" s="25"/>
       <c r="Z37" s="25" t="s">
@@ -8609,10 +8378,10 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="13.2">
-      <c r="A38" s="313"/>
-      <c r="B38" s="290"/>
-      <c r="C38" s="290"/>
-      <c r="D38" s="342"/>
+      <c r="A38" s="327"/>
+      <c r="B38" s="328"/>
+      <c r="C38" s="328"/>
+      <c r="D38" s="308"/>
       <c r="E38" s="104" t="s">
         <v>23</v>
       </c>
@@ -8662,10 +8431,10 @@
       <c r="Z38" s="25"/>
     </row>
     <row r="39" spans="1:26" ht="13.2">
-      <c r="A39" s="313"/>
-      <c r="B39" s="291"/>
-      <c r="C39" s="291"/>
-      <c r="D39" s="329"/>
+      <c r="A39" s="327"/>
+      <c r="B39" s="297"/>
+      <c r="C39" s="297"/>
+      <c r="D39" s="309"/>
       <c r="E39" s="104" t="s">
         <v>17</v>
       </c>
@@ -8717,8 +8486,8 @@
       <c r="Z39" s="25"/>
     </row>
     <row r="40" spans="1:26" ht="13.2">
-      <c r="A40" s="313"/>
-      <c r="B40" s="322" t="s">
+      <c r="A40" s="327"/>
+      <c r="B40" s="296" t="s">
         <v>145</v>
       </c>
       <c r="C40" s="98" t="s">
@@ -8789,9 +8558,9 @@
       </c>
     </row>
     <row r="41" spans="1:26" ht="13.2">
-      <c r="A41" s="313"/>
-      <c r="B41" s="290"/>
-      <c r="C41" s="322" t="s">
+      <c r="A41" s="327"/>
+      <c r="B41" s="328"/>
+      <c r="C41" s="296" t="s">
         <v>462</v>
       </c>
       <c r="D41" s="57" t="s">
@@ -8848,9 +8617,9 @@
       <c r="Z41" s="25"/>
     </row>
     <row r="42" spans="1:26" ht="13.2">
-      <c r="A42" s="313"/>
-      <c r="B42" s="290"/>
-      <c r="C42" s="291"/>
+      <c r="A42" s="327"/>
+      <c r="B42" s="328"/>
+      <c r="C42" s="297"/>
       <c r="D42" s="57" t="s">
         <v>125</v>
       </c>
@@ -8884,12 +8653,12 @@
       <c r="Z42" s="25"/>
     </row>
     <row r="43" spans="1:26" ht="13.2">
-      <c r="A43" s="313"/>
-      <c r="B43" s="290"/>
-      <c r="C43" s="337" t="s">
+      <c r="A43" s="327"/>
+      <c r="B43" s="328"/>
+      <c r="C43" s="311" t="s">
         <v>518</v>
       </c>
-      <c r="D43" s="366" t="s">
+      <c r="D43" s="313" t="s">
         <v>17</v>
       </c>
       <c r="E43" s="104" t="s">
@@ -8901,7 +8670,7 @@
       <c r="G43" s="193" t="s">
         <v>530</v>
       </c>
-      <c r="H43" s="365">
+      <c r="H43" s="290">
         <v>42</v>
       </c>
       <c r="I43" s="232">
@@ -8943,10 +8712,10 @@
       <c r="Z43" s="25"/>
     </row>
     <row r="44" spans="1:26" ht="13.2">
-      <c r="A44" s="313"/>
-      <c r="B44" s="291"/>
-      <c r="C44" s="339"/>
-      <c r="D44" s="367"/>
+      <c r="A44" s="327"/>
+      <c r="B44" s="297"/>
+      <c r="C44" s="312"/>
+      <c r="D44" s="314"/>
       <c r="E44" s="104" t="s">
         <v>23</v>
       </c>
@@ -8956,7 +8725,7 @@
       <c r="G44" s="193" t="s">
         <v>532</v>
       </c>
-      <c r="H44" s="365"/>
+      <c r="H44" s="290"/>
       <c r="I44" s="232">
         <v>1</v>
       </c>
@@ -8996,7 +8765,7 @@
       <c r="Z44" s="25"/>
     </row>
     <row r="45" spans="1:26" ht="92.4">
-      <c r="A45" s="313"/>
+      <c r="A45" s="327"/>
       <c r="B45" s="33" t="s">
         <v>148</v>
       </c>
@@ -9048,16 +8817,16 @@
       </c>
     </row>
     <row r="46" spans="1:26" ht="12.45" customHeight="1">
-      <c r="A46" s="343" t="s">
+      <c r="A46" s="293" t="s">
         <v>408</v>
       </c>
-      <c r="B46" s="323" t="s">
+      <c r="B46" s="300" t="s">
         <v>90</v>
       </c>
-      <c r="C46" s="322" t="s">
+      <c r="C46" s="296" t="s">
         <v>86</v>
       </c>
-      <c r="D46" s="346" t="s">
+      <c r="D46" s="298" t="s">
         <v>17</v>
       </c>
       <c r="E46" s="285" t="s">
@@ -9095,10 +8864,10 @@
       </c>
     </row>
     <row r="47" spans="1:26" ht="12.45" customHeight="1">
-      <c r="A47" s="344"/>
-      <c r="B47" s="349"/>
-      <c r="C47" s="291"/>
-      <c r="D47" s="347"/>
+      <c r="A47" s="294"/>
+      <c r="B47" s="303"/>
+      <c r="C47" s="297"/>
+      <c r="D47" s="299"/>
       <c r="E47" s="285" t="s">
         <v>17</v>
       </c>
@@ -9137,8 +8906,8 @@
       <c r="Z47" s="25"/>
     </row>
     <row r="48" spans="1:26" ht="13.2">
-      <c r="A48" s="344"/>
-      <c r="B48" s="321" t="s">
+      <c r="A48" s="294"/>
+      <c r="B48" s="305" t="s">
         <v>97</v>
       </c>
       <c r="C48" s="98" t="s">
@@ -9192,8 +8961,8 @@
       </c>
     </row>
     <row r="49" spans="1:26" ht="13.2">
-      <c r="A49" s="344"/>
-      <c r="B49" s="321"/>
+      <c r="A49" s="294"/>
+      <c r="B49" s="305"/>
       <c r="C49" s="98" t="s">
         <v>100</v>
       </c>
@@ -9245,8 +9014,8 @@
       </c>
     </row>
     <row r="50" spans="1:26" ht="13.2">
-      <c r="A50" s="344"/>
-      <c r="B50" s="321"/>
+      <c r="A50" s="294"/>
+      <c r="B50" s="305"/>
       <c r="C50" s="98" t="s">
         <v>101</v>
       </c>
@@ -9298,8 +9067,8 @@
       </c>
     </row>
     <row r="51" spans="1:26" ht="13.2">
-      <c r="A51" s="344"/>
-      <c r="B51" s="321"/>
+      <c r="A51" s="294"/>
+      <c r="B51" s="305"/>
       <c r="C51" s="98" t="s">
         <v>102</v>
       </c>
@@ -9347,14 +9116,14 @@
       </c>
     </row>
     <row r="52" spans="1:26" ht="26.4">
-      <c r="A52" s="344"/>
-      <c r="B52" s="323" t="s">
+      <c r="A52" s="294"/>
+      <c r="B52" s="300" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="322" t="s">
+      <c r="C52" s="296" t="s">
         <v>104</v>
       </c>
-      <c r="D52" s="346" t="s">
+      <c r="D52" s="298" t="s">
         <v>17</v>
       </c>
       <c r="E52" s="285" t="s">
@@ -9388,10 +9157,10 @@
       <c r="Z52" s="25"/>
     </row>
     <row r="53" spans="1:26" ht="13.2">
-      <c r="A53" s="344"/>
-      <c r="B53" s="324"/>
-      <c r="C53" s="291"/>
-      <c r="D53" s="347"/>
+      <c r="A53" s="294"/>
+      <c r="B53" s="301"/>
+      <c r="C53" s="297"/>
+      <c r="D53" s="299"/>
       <c r="E53" s="285" t="s">
         <v>17</v>
       </c>
@@ -9437,12 +9206,12 @@
       </c>
     </row>
     <row r="54" spans="1:26" ht="25.05" customHeight="1">
-      <c r="A54" s="344"/>
-      <c r="B54" s="324"/>
-      <c r="C54" s="322" t="s">
+      <c r="A54" s="294"/>
+      <c r="B54" s="301"/>
+      <c r="C54" s="296" t="s">
         <v>109</v>
       </c>
-      <c r="D54" s="346" t="s">
+      <c r="D54" s="298" t="s">
         <v>17</v>
       </c>
       <c r="E54" s="285" t="s">
@@ -9480,10 +9249,10 @@
       </c>
     </row>
     <row r="55" spans="1:26" ht="13.2">
-      <c r="A55" s="344"/>
-      <c r="B55" s="324"/>
-      <c r="C55" s="291"/>
-      <c r="D55" s="347"/>
+      <c r="A55" s="294"/>
+      <c r="B55" s="301"/>
+      <c r="C55" s="297"/>
+      <c r="D55" s="299"/>
       <c r="E55" s="285" t="s">
         <v>17</v>
       </c>
@@ -9522,12 +9291,12 @@
       <c r="Z55" s="25"/>
     </row>
     <row r="56" spans="1:26" ht="26.4">
-      <c r="A56" s="344"/>
-      <c r="B56" s="324"/>
-      <c r="C56" s="322" t="s">
+      <c r="A56" s="294"/>
+      <c r="B56" s="301"/>
+      <c r="C56" s="296" t="s">
         <v>110</v>
       </c>
-      <c r="D56" s="346" t="s">
+      <c r="D56" s="298" t="s">
         <v>17</v>
       </c>
       <c r="E56" s="285" t="s">
@@ -9565,10 +9334,10 @@
       </c>
     </row>
     <row r="57" spans="1:26" ht="13.2">
-      <c r="A57" s="344"/>
-      <c r="B57" s="324"/>
-      <c r="C57" s="291"/>
-      <c r="D57" s="347"/>
+      <c r="A57" s="294"/>
+      <c r="B57" s="301"/>
+      <c r="C57" s="297"/>
+      <c r="D57" s="299"/>
       <c r="E57" s="286" t="s">
         <v>17</v>
       </c>
@@ -9610,12 +9379,12 @@
       <c r="Z57" s="25"/>
     </row>
     <row r="58" spans="1:26" ht="13.2">
-      <c r="A58" s="344"/>
-      <c r="B58" s="324"/>
-      <c r="C58" s="368" t="s">
+      <c r="A58" s="294"/>
+      <c r="B58" s="301"/>
+      <c r="C58" s="291" t="s">
         <v>533</v>
       </c>
-      <c r="D58" s="369" t="s">
+      <c r="D58" s="292" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="286" t="s">
@@ -9644,10 +9413,10 @@
       <c r="Z58" s="25"/>
     </row>
     <row r="59" spans="1:26" ht="13.2">
-      <c r="A59" s="344"/>
-      <c r="B59" s="324"/>
-      <c r="C59" s="368"/>
-      <c r="D59" s="369"/>
+      <c r="A59" s="294"/>
+      <c r="B59" s="301"/>
+      <c r="C59" s="291"/>
+      <c r="D59" s="292"/>
       <c r="E59" s="286"/>
       <c r="F59" s="264"/>
       <c r="G59" s="239"/>
@@ -9672,8 +9441,8 @@
       <c r="Z59" s="25"/>
     </row>
     <row r="60" spans="1:26" ht="13.2">
-      <c r="A60" s="344"/>
-      <c r="B60" s="348"/>
+      <c r="A60" s="294"/>
+      <c r="B60" s="302"/>
       <c r="C60" s="183" t="s">
         <v>111</v>
       </c>
@@ -9725,14 +9494,14 @@
       </c>
     </row>
     <row r="61" spans="1:26" ht="13.95" customHeight="1">
-      <c r="A61" s="344"/>
-      <c r="B61" s="334" t="s">
+      <c r="A61" s="294"/>
+      <c r="B61" s="306" t="s">
         <v>112</v>
       </c>
-      <c r="C61" s="334" t="s">
+      <c r="C61" s="306" t="s">
         <v>86</v>
       </c>
-      <c r="D61" s="341" t="s">
+      <c r="D61" s="304" t="s">
         <v>17</v>
       </c>
       <c r="E61" s="273" t="s">
@@ -9791,10 +9560,10 @@
       </c>
     </row>
     <row r="62" spans="1:26" ht="12.45" customHeight="1">
-      <c r="A62" s="344"/>
-      <c r="B62" s="334"/>
-      <c r="C62" s="334"/>
-      <c r="D62" s="341"/>
+      <c r="A62" s="294"/>
+      <c r="B62" s="306"/>
+      <c r="C62" s="306"/>
+      <c r="D62" s="304"/>
       <c r="E62" s="273" t="s">
         <v>17</v>
       </c>
@@ -9847,12 +9616,12 @@
       <c r="Z62" s="25"/>
     </row>
     <row r="63" spans="1:26" ht="17.55" customHeight="1">
-      <c r="A63" s="344"/>
-      <c r="B63" s="334"/>
-      <c r="C63" s="334" t="s">
+      <c r="A63" s="294"/>
+      <c r="B63" s="306"/>
+      <c r="C63" s="306" t="s">
         <v>116</v>
       </c>
-      <c r="D63" s="341" t="s">
+      <c r="D63" s="304" t="s">
         <v>17</v>
       </c>
       <c r="E63" s="273" t="s">
@@ -9911,10 +9680,10 @@
       </c>
     </row>
     <row r="64" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A64" s="344"/>
-      <c r="B64" s="334"/>
-      <c r="C64" s="334"/>
-      <c r="D64" s="341"/>
+      <c r="A64" s="294"/>
+      <c r="B64" s="306"/>
+      <c r="C64" s="306"/>
+      <c r="D64" s="304"/>
       <c r="E64" s="273" t="s">
         <v>23</v>
       </c>
@@ -9967,10 +9736,10 @@
       <c r="Z64" s="25"/>
     </row>
     <row r="65" spans="1:26" ht="12.45" customHeight="1">
-      <c r="A65" s="344"/>
-      <c r="B65" s="334"/>
-      <c r="C65" s="334"/>
-      <c r="D65" s="341"/>
+      <c r="A65" s="294"/>
+      <c r="B65" s="306"/>
+      <c r="C65" s="306"/>
+      <c r="D65" s="304"/>
       <c r="E65" s="273" t="s">
         <v>23</v>
       </c>
@@ -10023,10 +9792,10 @@
       <c r="Z65" s="25"/>
     </row>
     <row r="66" spans="1:26" ht="13.05" customHeight="1">
-      <c r="A66" s="344"/>
-      <c r="B66" s="334"/>
-      <c r="C66" s="334"/>
-      <c r="D66" s="341"/>
+      <c r="A66" s="294"/>
+      <c r="B66" s="306"/>
+      <c r="C66" s="306"/>
+      <c r="D66" s="304"/>
       <c r="E66" s="273" t="s">
         <v>23</v>
       </c>
@@ -10079,10 +9848,10 @@
       <c r="Z66" s="25"/>
     </row>
     <row r="67" spans="1:26" ht="13.05" customHeight="1">
-      <c r="A67" s="344"/>
-      <c r="B67" s="334"/>
-      <c r="C67" s="334"/>
-      <c r="D67" s="341"/>
+      <c r="A67" s="294"/>
+      <c r="B67" s="306"/>
+      <c r="C67" s="306"/>
+      <c r="D67" s="304"/>
       <c r="E67" s="273" t="s">
         <v>17</v>
       </c>
@@ -10133,12 +9902,12 @@
       <c r="Z67" s="25"/>
     </row>
     <row r="68" spans="1:26" ht="15" customHeight="1">
-      <c r="A68" s="344"/>
-      <c r="B68" s="334"/>
-      <c r="C68" s="334" t="s">
+      <c r="A68" s="294"/>
+      <c r="B68" s="306"/>
+      <c r="C68" s="306" t="s">
         <v>120</v>
       </c>
-      <c r="D68" s="340" t="s">
+      <c r="D68" s="310" t="s">
         <v>17</v>
       </c>
       <c r="E68" s="273" t="s">
@@ -10197,10 +9966,10 @@
       </c>
     </row>
     <row r="69" spans="1:26" ht="13.05" customHeight="1">
-      <c r="A69" s="344"/>
-      <c r="B69" s="334"/>
-      <c r="C69" s="334"/>
-      <c r="D69" s="340"/>
+      <c r="A69" s="294"/>
+      <c r="B69" s="306"/>
+      <c r="C69" s="306"/>
+      <c r="D69" s="310"/>
       <c r="E69" s="273" t="s">
         <v>23</v>
       </c>
@@ -10253,10 +10022,10 @@
       <c r="Z69" s="25"/>
     </row>
     <row r="70" spans="1:26" ht="14.55" customHeight="1">
-      <c r="A70" s="344"/>
-      <c r="B70" s="334"/>
-      <c r="C70" s="334"/>
-      <c r="D70" s="340"/>
+      <c r="A70" s="294"/>
+      <c r="B70" s="306"/>
+      <c r="C70" s="306"/>
+      <c r="D70" s="310"/>
       <c r="E70" s="273" t="s">
         <v>17</v>
       </c>
@@ -10306,8 +10075,8 @@
       <c r="Z70" s="25"/>
     </row>
     <row r="71" spans="1:26" ht="13.2">
-      <c r="A71" s="344"/>
-      <c r="B71" s="336" t="s">
+      <c r="A71" s="294"/>
+      <c r="B71" s="316" t="s">
         <v>122</v>
       </c>
       <c r="C71" s="203" t="s">
@@ -10372,8 +10141,8 @@
       </c>
     </row>
     <row r="72" spans="1:26" ht="13.2">
-      <c r="A72" s="344"/>
-      <c r="B72" s="336"/>
+      <c r="A72" s="294"/>
+      <c r="B72" s="316"/>
       <c r="C72" s="203" t="s">
         <v>123</v>
       </c>
@@ -10436,8 +10205,8 @@
       </c>
     </row>
     <row r="73" spans="1:26" ht="13.2">
-      <c r="A73" s="344"/>
-      <c r="B73" s="336"/>
+      <c r="A73" s="294"/>
+      <c r="B73" s="316"/>
       <c r="C73" s="203" t="s">
         <v>126</v>
       </c>
@@ -10500,11 +10269,11 @@
       </c>
     </row>
     <row r="74" spans="1:26" ht="13.2">
-      <c r="A74" s="344"/>
-      <c r="B74" s="336" t="s">
+      <c r="A74" s="294"/>
+      <c r="B74" s="316" t="s">
         <v>128</v>
       </c>
-      <c r="C74" s="334" t="s">
+      <c r="C74" s="306" t="s">
         <v>86</v>
       </c>
       <c r="D74" s="273" t="s">
@@ -10566,9 +10335,9 @@
       </c>
     </row>
     <row r="75" spans="1:26" ht="13.2">
-      <c r="A75" s="344"/>
-      <c r="B75" s="336"/>
-      <c r="C75" s="334"/>
+      <c r="A75" s="294"/>
+      <c r="B75" s="316"/>
+      <c r="C75" s="306"/>
       <c r="D75" s="273" t="s">
         <v>17</v>
       </c>
@@ -10624,12 +10393,12 @@
       <c r="Z75" s="25"/>
     </row>
     <row r="76" spans="1:26" ht="13.2">
-      <c r="A76" s="344"/>
-      <c r="B76" s="336"/>
-      <c r="C76" s="335" t="s">
+      <c r="A76" s="294"/>
+      <c r="B76" s="316"/>
+      <c r="C76" s="315" t="s">
         <v>129</v>
       </c>
-      <c r="D76" s="340" t="s">
+      <c r="D76" s="310" t="s">
         <v>17</v>
       </c>
       <c r="E76" s="273" t="s">
@@ -10684,10 +10453,10 @@
       <c r="Z76" s="25"/>
     </row>
     <row r="77" spans="1:26" ht="13.2">
-      <c r="A77" s="344"/>
-      <c r="B77" s="336"/>
-      <c r="C77" s="335"/>
-      <c r="D77" s="340"/>
+      <c r="A77" s="294"/>
+      <c r="B77" s="316"/>
+      <c r="C77" s="315"/>
+      <c r="D77" s="310"/>
       <c r="E77" s="273" t="s">
         <v>23</v>
       </c>
@@ -10744,10 +10513,10 @@
       </c>
     </row>
     <row r="78" spans="1:26" ht="13.2">
-      <c r="A78" s="344"/>
-      <c r="B78" s="336"/>
-      <c r="C78" s="335"/>
-      <c r="D78" s="340"/>
+      <c r="A78" s="294"/>
+      <c r="B78" s="316"/>
+      <c r="C78" s="315"/>
+      <c r="D78" s="310"/>
       <c r="E78" s="273" t="s">
         <v>17</v>
       </c>
@@ -10797,12 +10566,12 @@
       <c r="Z78" s="25"/>
     </row>
     <row r="79" spans="1:26" ht="13.2">
-      <c r="A79" s="344"/>
-      <c r="B79" s="336"/>
-      <c r="C79" s="334" t="s">
+      <c r="A79" s="294"/>
+      <c r="B79" s="316"/>
+      <c r="C79" s="306" t="s">
         <v>132</v>
       </c>
-      <c r="D79" s="340" t="s">
+      <c r="D79" s="310" t="s">
         <v>17</v>
       </c>
       <c r="E79" s="273" t="s">
@@ -10861,10 +10630,10 @@
       </c>
     </row>
     <row r="80" spans="1:26" ht="13.2">
-      <c r="A80" s="344"/>
-      <c r="B80" s="336"/>
-      <c r="C80" s="334"/>
-      <c r="D80" s="340"/>
+      <c r="A80" s="294"/>
+      <c r="B80" s="316"/>
+      <c r="C80" s="306"/>
+      <c r="D80" s="310"/>
       <c r="E80" s="273" t="s">
         <v>17</v>
       </c>
@@ -10914,12 +10683,12 @@
       <c r="Z80" s="25"/>
     </row>
     <row r="81" spans="1:26" ht="13.2">
-      <c r="A81" s="344"/>
-      <c r="B81" s="336"/>
-      <c r="C81" s="334" t="s">
+      <c r="A81" s="294"/>
+      <c r="B81" s="316"/>
+      <c r="C81" s="306" t="s">
         <v>133</v>
       </c>
-      <c r="D81" s="340" t="s">
+      <c r="D81" s="310" t="s">
         <v>17</v>
       </c>
       <c r="E81" s="273" t="s">
@@ -10971,10 +10740,10 @@
       <c r="Z81" s="25"/>
     </row>
     <row r="82" spans="1:26" ht="13.2">
-      <c r="A82" s="344"/>
-      <c r="B82" s="336"/>
-      <c r="C82" s="334"/>
-      <c r="D82" s="340"/>
+      <c r="A82" s="294"/>
+      <c r="B82" s="316"/>
+      <c r="C82" s="306"/>
+      <c r="D82" s="310"/>
       <c r="E82" s="273" t="s">
         <v>23</v>
       </c>
@@ -11031,10 +10800,10 @@
       </c>
     </row>
     <row r="83" spans="1:26" ht="13.2">
-      <c r="A83" s="344"/>
-      <c r="B83" s="336"/>
-      <c r="C83" s="334"/>
-      <c r="D83" s="340"/>
+      <c r="A83" s="294"/>
+      <c r="B83" s="316"/>
+      <c r="C83" s="306"/>
+      <c r="D83" s="310"/>
       <c r="E83" s="273" t="s">
         <v>17</v>
       </c>
@@ -11084,14 +10853,14 @@
       <c r="Z83" s="25"/>
     </row>
     <row r="84" spans="1:26" ht="13.2">
-      <c r="A84" s="344"/>
-      <c r="B84" s="334" t="s">
+      <c r="A84" s="294"/>
+      <c r="B84" s="306" t="s">
         <v>134</v>
       </c>
-      <c r="C84" s="334" t="s">
+      <c r="C84" s="306" t="s">
         <v>86</v>
       </c>
-      <c r="D84" s="341" t="s">
+      <c r="D84" s="304" t="s">
         <v>17</v>
       </c>
       <c r="E84" s="273" t="s">
@@ -11147,10 +10916,10 @@
       </c>
     </row>
     <row r="85" spans="1:26" ht="13.2">
-      <c r="A85" s="344"/>
-      <c r="B85" s="334"/>
-      <c r="C85" s="334"/>
-      <c r="D85" s="341"/>
+      <c r="A85" s="294"/>
+      <c r="B85" s="306"/>
+      <c r="C85" s="306"/>
+      <c r="D85" s="304"/>
       <c r="E85" s="273" t="s">
         <v>23</v>
       </c>
@@ -11200,10 +10969,10 @@
       <c r="Z85" s="25"/>
     </row>
     <row r="86" spans="1:26" ht="13.2">
-      <c r="A86" s="344"/>
-      <c r="B86" s="334"/>
-      <c r="C86" s="334"/>
-      <c r="D86" s="341"/>
+      <c r="A86" s="294"/>
+      <c r="B86" s="306"/>
+      <c r="C86" s="306"/>
+      <c r="D86" s="304"/>
       <c r="E86" s="273" t="s">
         <v>17</v>
       </c>
@@ -11253,8 +11022,8 @@
       <c r="Z86" s="25"/>
     </row>
     <row r="87" spans="1:26" ht="13.2">
-      <c r="A87" s="344"/>
-      <c r="B87" s="334"/>
+      <c r="A87" s="294"/>
+      <c r="B87" s="306"/>
       <c r="C87" s="203" t="s">
         <v>135</v>
       </c>
@@ -11315,12 +11084,12 @@
       </c>
     </row>
     <row r="88" spans="1:26" ht="13.2">
-      <c r="A88" s="344"/>
-      <c r="B88" s="334"/>
-      <c r="C88" s="334" t="s">
+      <c r="A88" s="294"/>
+      <c r="B88" s="306"/>
+      <c r="C88" s="306" t="s">
         <v>140</v>
       </c>
-      <c r="D88" s="341" t="s">
+      <c r="D88" s="304" t="s">
         <v>17</v>
       </c>
       <c r="E88" s="273" t="s">
@@ -11377,10 +11146,10 @@
       </c>
     </row>
     <row r="89" spans="1:26" ht="13.2">
-      <c r="A89" s="344"/>
-      <c r="B89" s="334"/>
-      <c r="C89" s="334"/>
-      <c r="D89" s="341"/>
+      <c r="A89" s="294"/>
+      <c r="B89" s="306"/>
+      <c r="C89" s="306"/>
+      <c r="D89" s="304"/>
       <c r="E89" s="273" t="s">
         <v>17</v>
       </c>
@@ -11430,8 +11199,8 @@
       <c r="Z89" s="25"/>
     </row>
     <row r="90" spans="1:26" ht="13.2">
-      <c r="A90" s="344"/>
-      <c r="B90" s="334"/>
+      <c r="A90" s="294"/>
+      <c r="B90" s="306"/>
       <c r="C90" s="203" t="s">
         <v>142</v>
       </c>
@@ -11469,12 +11238,12 @@
       </c>
     </row>
     <row r="91" spans="1:26" ht="13.2">
-      <c r="A91" s="344"/>
-      <c r="B91" s="334"/>
-      <c r="C91" s="334" t="s">
+      <c r="A91" s="294"/>
+      <c r="B91" s="306"/>
+      <c r="C91" s="306" t="s">
         <v>143</v>
       </c>
-      <c r="D91" s="341" t="s">
+      <c r="D91" s="304" t="s">
         <v>17</v>
       </c>
       <c r="E91" s="273" t="s">
@@ -11531,10 +11300,10 @@
       </c>
     </row>
     <row r="92" spans="1:26" ht="13.2">
-      <c r="A92" s="344"/>
-      <c r="B92" s="334"/>
-      <c r="C92" s="334"/>
-      <c r="D92" s="341"/>
+      <c r="A92" s="294"/>
+      <c r="B92" s="306"/>
+      <c r="C92" s="306"/>
+      <c r="D92" s="304"/>
       <c r="E92" s="273" t="s">
         <v>17</v>
       </c>
@@ -11584,8 +11353,8 @@
       <c r="Z92" s="25"/>
     </row>
     <row r="93" spans="1:26" ht="13.2">
-      <c r="A93" s="344"/>
-      <c r="B93" s="334"/>
+      <c r="A93" s="294"/>
+      <c r="B93" s="306"/>
       <c r="C93" s="203" t="s">
         <v>144</v>
       </c>
@@ -11646,8 +11415,8 @@
       </c>
     </row>
     <row r="94" spans="1:26" ht="13.2">
-      <c r="A94" s="344"/>
-      <c r="B94" s="337" t="s">
+      <c r="A94" s="294"/>
+      <c r="B94" s="311" t="s">
         <v>146</v>
       </c>
       <c r="C94" s="203" t="s">
@@ -11686,8 +11455,8 @@
       <c r="Z94" s="25"/>
     </row>
     <row r="95" spans="1:26" ht="13.2">
-      <c r="A95" s="344"/>
-      <c r="B95" s="338"/>
+      <c r="A95" s="294"/>
+      <c r="B95" s="321"/>
       <c r="C95" s="203" t="s">
         <v>506</v>
       </c>
@@ -11724,8 +11493,8 @@
       <c r="Z95" s="25"/>
     </row>
     <row r="96" spans="1:26" ht="13.2">
-      <c r="A96" s="345"/>
-      <c r="B96" s="339"/>
+      <c r="A96" s="295"/>
+      <c r="B96" s="312"/>
       <c r="C96" s="203" t="s">
         <v>507</v>
       </c>
@@ -11806,13 +11575,13 @@
       </c>
     </row>
     <row r="98" spans="1:26" ht="13.2">
-      <c r="A98" s="313" t="s">
+      <c r="A98" s="327" t="s">
         <v>12</v>
       </c>
-      <c r="B98" s="294" t="s">
+      <c r="B98" s="319" t="s">
         <v>175</v>
       </c>
-      <c r="C98" s="305" t="s">
+      <c r="C98" s="317" t="s">
         <v>176</v>
       </c>
       <c r="D98" s="189" t="s">
@@ -11883,9 +11652,9 @@
       </c>
     </row>
     <row r="99" spans="1:26" ht="13.2">
-      <c r="A99" s="314"/>
-      <c r="B99" s="294"/>
-      <c r="C99" s="306"/>
+      <c r="A99" s="334"/>
+      <c r="B99" s="319"/>
+      <c r="C99" s="349"/>
       <c r="D99" t="s">
         <v>17</v>
       </c>
@@ -11938,9 +11707,9 @@
       <c r="Z99" s="25"/>
     </row>
     <row r="100" spans="1:26" ht="13.2">
-      <c r="A100" s="314"/>
-      <c r="B100" s="294"/>
-      <c r="C100" s="307"/>
+      <c r="A100" s="334"/>
+      <c r="B100" s="319"/>
+      <c r="C100" s="318"/>
       <c r="D100" s="189" t="s">
         <v>17</v>
       </c>
@@ -11993,8 +11762,8 @@
       <c r="Z100" s="25"/>
     </row>
     <row r="101" spans="1:26" ht="13.2">
-      <c r="A101" s="314"/>
-      <c r="B101" s="294"/>
+      <c r="A101" s="334"/>
+      <c r="B101" s="319"/>
       <c r="C101" s="98" t="s">
         <v>183</v>
       </c>
@@ -12066,11 +11835,11 @@
       </c>
     </row>
     <row r="102" spans="1:26" ht="13.2">
-      <c r="A102" s="314"/>
-      <c r="B102" s="294" t="s">
+      <c r="A102" s="334"/>
+      <c r="B102" s="319" t="s">
         <v>188</v>
       </c>
-      <c r="C102" s="305" t="s">
+      <c r="C102" s="317" t="s">
         <v>176</v>
       </c>
       <c r="D102" s="189" t="s">
@@ -12141,9 +11910,9 @@
       </c>
     </row>
     <row r="103" spans="1:26" ht="13.2">
-      <c r="A103" s="314"/>
-      <c r="B103" s="292"/>
-      <c r="C103" s="307"/>
+      <c r="A103" s="334"/>
+      <c r="B103" s="320"/>
+      <c r="C103" s="318"/>
       <c r="D103" t="s">
         <v>125</v>
       </c>
@@ -12196,8 +11965,8 @@
       <c r="Z103" s="25"/>
     </row>
     <row r="104" spans="1:26" ht="13.2">
-      <c r="A104" s="314"/>
-      <c r="B104" s="292"/>
+      <c r="A104" s="334"/>
+      <c r="B104" s="320"/>
       <c r="C104" s="98" t="s">
         <v>189</v>
       </c>
@@ -12257,9 +12026,9 @@
       </c>
     </row>
     <row r="105" spans="1:26" ht="13.2">
-      <c r="A105" s="314"/>
-      <c r="B105" s="294"/>
-      <c r="C105" s="305" t="s">
+      <c r="A105" s="334"/>
+      <c r="B105" s="319"/>
+      <c r="C105" s="317" t="s">
         <v>192</v>
       </c>
       <c r="D105" s="189" t="s">
@@ -12330,9 +12099,9 @@
       </c>
     </row>
     <row r="106" spans="1:26" ht="13.2">
-      <c r="A106" s="314"/>
-      <c r="B106" s="294"/>
-      <c r="C106" s="307"/>
+      <c r="A106" s="334"/>
+      <c r="B106" s="319"/>
+      <c r="C106" s="318"/>
       <c r="D106" s="189" t="s">
         <v>17</v>
       </c>
@@ -12384,8 +12153,8 @@
       <c r="Y106" s="40"/>
     </row>
     <row r="107" spans="1:26" ht="13.2">
-      <c r="A107" s="314"/>
-      <c r="B107" s="294"/>
+      <c r="A107" s="334"/>
+      <c r="B107" s="319"/>
       <c r="C107" s="98" t="s">
         <v>196</v>
       </c>
@@ -12443,9 +12212,9 @@
       </c>
     </row>
     <row r="108" spans="1:26" ht="13.2">
-      <c r="A108" s="314"/>
-      <c r="B108" s="294"/>
-      <c r="C108" s="299" t="s">
+      <c r="A108" s="334"/>
+      <c r="B108" s="319"/>
+      <c r="C108" s="343" t="s">
         <v>197</v>
       </c>
       <c r="D108" s="189" t="s">
@@ -12502,9 +12271,9 @@
       </c>
     </row>
     <row r="109" spans="1:26" ht="13.2">
-      <c r="A109" s="314"/>
-      <c r="B109" s="294"/>
-      <c r="C109" s="302"/>
+      <c r="A109" s="334"/>
+      <c r="B109" s="319"/>
+      <c r="C109" s="346"/>
       <c r="D109" s="208" t="s">
         <v>17</v>
       </c>
@@ -12559,11 +12328,11 @@
       </c>
     </row>
     <row r="110" spans="1:26" ht="13.2">
-      <c r="A110" s="314"/>
-      <c r="B110" s="316" t="s">
+      <c r="A110" s="334"/>
+      <c r="B110" s="339" t="s">
         <v>200</v>
       </c>
-      <c r="C110" s="308" t="s">
+      <c r="C110" s="350" t="s">
         <v>470</v>
       </c>
       <c r="D110" s="105" t="s">
@@ -12617,9 +12386,9 @@
       </c>
     </row>
     <row r="111" spans="1:26" ht="13.2">
-      <c r="A111" s="314"/>
-      <c r="B111" s="317"/>
-      <c r="C111" s="309"/>
+      <c r="A111" s="334"/>
+      <c r="B111" s="340"/>
+      <c r="C111" s="351"/>
       <c r="D111" s="105" t="s">
         <v>17</v>
       </c>
@@ -12669,9 +12438,9 @@
       <c r="Z111"/>
     </row>
     <row r="112" spans="1:26" ht="13.2">
-      <c r="A112" s="314"/>
-      <c r="B112" s="317"/>
-      <c r="C112" s="310"/>
+      <c r="A112" s="334"/>
+      <c r="B112" s="340"/>
+      <c r="C112" s="352"/>
       <c r="D112" s="105" t="s">
         <v>17</v>
       </c>
@@ -12721,9 +12490,9 @@
       <c r="Z112"/>
     </row>
     <row r="113" spans="1:26" ht="13.2">
-      <c r="A113" s="314"/>
-      <c r="B113" s="318"/>
-      <c r="C113" s="308" t="s">
+      <c r="A113" s="334"/>
+      <c r="B113" s="341"/>
+      <c r="C113" s="350" t="s">
         <v>469</v>
       </c>
       <c r="D113" s="105" t="s">
@@ -12777,9 +12546,9 @@
       </c>
     </row>
     <row r="114" spans="1:26" ht="13.2">
-      <c r="A114" s="314"/>
-      <c r="B114" s="318"/>
-      <c r="C114" s="309"/>
+      <c r="A114" s="334"/>
+      <c r="B114" s="341"/>
+      <c r="C114" s="351"/>
       <c r="D114" s="105" t="s">
         <v>17</v>
       </c>
@@ -12829,9 +12598,9 @@
       <c r="Z114"/>
     </row>
     <row r="115" spans="1:26" ht="13.2">
-      <c r="A115" s="314"/>
-      <c r="B115" s="318"/>
-      <c r="C115" s="310"/>
+      <c r="A115" s="334"/>
+      <c r="B115" s="341"/>
+      <c r="C115" s="352"/>
       <c r="D115" s="105" t="s">
         <v>17</v>
       </c>
@@ -12881,8 +12650,8 @@
       <c r="Z115"/>
     </row>
     <row r="116" spans="1:26" ht="13.2">
-      <c r="A116" s="314"/>
-      <c r="B116" s="318"/>
+      <c r="A116" s="334"/>
+      <c r="B116" s="341"/>
       <c r="C116" t="s">
         <v>456</v>
       </c>
@@ -12935,8 +12704,8 @@
       <c r="Z116"/>
     </row>
     <row r="117" spans="1:26" ht="13.2">
-      <c r="A117" s="314"/>
-      <c r="B117" s="318"/>
+      <c r="A117" s="334"/>
+      <c r="B117" s="341"/>
       <c r="C117" t="s">
         <v>457</v>
       </c>
@@ -12989,8 +12758,8 @@
       <c r="Z117"/>
     </row>
     <row r="118" spans="1:26" ht="13.2">
-      <c r="A118" s="314"/>
-      <c r="B118" s="318"/>
+      <c r="A118" s="334"/>
+      <c r="B118" s="341"/>
       <c r="C118" t="s">
         <v>458</v>
       </c>
@@ -13043,8 +12812,8 @@
       <c r="Z118"/>
     </row>
     <row r="119" spans="1:26" ht="26.4">
-      <c r="A119" s="314"/>
-      <c r="B119" s="318"/>
+      <c r="A119" s="334"/>
+      <c r="B119" s="341"/>
       <c r="C119" s="205" t="s">
         <v>452</v>
       </c>
@@ -13097,8 +12866,8 @@
       <c r="Z119"/>
     </row>
     <row r="120" spans="1:26" ht="26.4">
-      <c r="A120" s="315"/>
-      <c r="B120" s="319"/>
+      <c r="A120" s="335"/>
+      <c r="B120" s="342"/>
       <c r="C120" s="205" t="s">
         <v>453</v>
       </c>
@@ -13151,10 +12920,10 @@
       <c r="Z120"/>
     </row>
     <row r="121" spans="1:26" ht="13.2">
-      <c r="A121" s="313" t="s">
+      <c r="A121" s="327" t="s">
         <v>11</v>
       </c>
-      <c r="B121" s="294" t="s">
+      <c r="B121" s="319" t="s">
         <v>201</v>
       </c>
       <c r="C121" s="198" t="s">
@@ -13202,9 +12971,9 @@
       </c>
     </row>
     <row r="122" spans="1:26" ht="13.2">
-      <c r="A122" s="314"/>
-      <c r="B122" s="292"/>
-      <c r="C122" s="303" t="s">
+      <c r="A122" s="334"/>
+      <c r="B122" s="320"/>
+      <c r="C122" s="347" t="s">
         <v>206</v>
       </c>
       <c r="D122" s="104" t="s">
@@ -13257,9 +13026,9 @@
       <c r="Z122" s="43"/>
     </row>
     <row r="123" spans="1:26" ht="13.2">
-      <c r="A123" s="314"/>
-      <c r="B123" s="292"/>
-      <c r="C123" s="304"/>
+      <c r="A123" s="334"/>
+      <c r="B123" s="320"/>
+      <c r="C123" s="348"/>
       <c r="D123" s="104" t="s">
         <v>17</v>
       </c>
@@ -13318,9 +13087,9 @@
       </c>
     </row>
     <row r="124" spans="1:26" ht="13.2">
-      <c r="A124" s="314"/>
-      <c r="B124" s="292"/>
-      <c r="C124" s="301" t="s">
+      <c r="A124" s="334"/>
+      <c r="B124" s="320"/>
+      <c r="C124" s="345" t="s">
         <v>211</v>
       </c>
       <c r="D124" s="104" t="s">
@@ -13373,9 +13142,9 @@
       <c r="Z124" s="25"/>
     </row>
     <row r="125" spans="1:26" ht="13.2">
-      <c r="A125" s="314"/>
-      <c r="B125" s="292"/>
-      <c r="C125" s="301"/>
+      <c r="A125" s="334"/>
+      <c r="B125" s="320"/>
+      <c r="C125" s="345"/>
       <c r="D125" s="105" t="s">
         <v>212</v>
       </c>
@@ -13426,9 +13195,9 @@
       <c r="Z125" s="25"/>
     </row>
     <row r="126" spans="1:26" ht="13.2">
-      <c r="A126" s="314"/>
-      <c r="B126" s="292"/>
-      <c r="C126" s="302"/>
+      <c r="A126" s="334"/>
+      <c r="B126" s="320"/>
+      <c r="C126" s="346"/>
       <c r="D126" s="222" t="s">
         <v>212</v>
       </c>
@@ -13479,9 +13248,9 @@
       <c r="Z126" s="25"/>
     </row>
     <row r="127" spans="1:26" ht="13.2">
-      <c r="A127" s="314"/>
-      <c r="B127" s="296"/>
-      <c r="C127" s="300"/>
+      <c r="A127" s="334"/>
+      <c r="B127" s="336"/>
+      <c r="C127" s="344"/>
       <c r="D127" s="105" t="s">
         <v>212</v>
       </c>
@@ -13542,11 +13311,11 @@
       </c>
     </row>
     <row r="128" spans="1:26" ht="13.2">
-      <c r="A128" s="314"/>
-      <c r="B128" s="294" t="s">
+      <c r="A128" s="334"/>
+      <c r="B128" s="319" t="s">
         <v>216</v>
       </c>
-      <c r="C128" s="299" t="s">
+      <c r="C128" s="343" t="s">
         <v>217</v>
       </c>
       <c r="D128" s="104" t="s">
@@ -13605,9 +13374,9 @@
       </c>
     </row>
     <row r="129" spans="1:26" ht="13.2">
-      <c r="A129" s="314"/>
-      <c r="B129" s="292"/>
-      <c r="C129" s="300"/>
+      <c r="A129" s="334"/>
+      <c r="B129" s="320"/>
+      <c r="C129" s="344"/>
       <c r="D129" s="104" t="s">
         <v>17</v>
       </c>
@@ -13658,9 +13427,9 @@
       <c r="Z129" s="25"/>
     </row>
     <row r="130" spans="1:26" ht="13.2">
-      <c r="A130" s="314"/>
-      <c r="B130" s="295"/>
-      <c r="C130" s="299" t="s">
+      <c r="A130" s="334"/>
+      <c r="B130" s="338"/>
+      <c r="C130" s="343" t="s">
         <v>221</v>
       </c>
       <c r="D130" s="104" t="s">
@@ -13723,9 +13492,9 @@
       </c>
     </row>
     <row r="131" spans="1:26" ht="13.2">
-      <c r="A131" s="314"/>
-      <c r="B131" s="295"/>
-      <c r="C131" s="300"/>
+      <c r="A131" s="334"/>
+      <c r="B131" s="338"/>
+      <c r="C131" s="344"/>
       <c r="D131" s="104" t="s">
         <v>17</v>
       </c>
@@ -13786,8 +13555,8 @@
       </c>
     </row>
     <row r="132" spans="1:26" ht="13.2">
-      <c r="A132" s="314"/>
-      <c r="B132" s="296"/>
+      <c r="A132" s="334"/>
+      <c r="B132" s="336"/>
       <c r="C132" s="98" t="s">
         <v>223</v>
       </c>
@@ -13847,11 +13616,11 @@
       </c>
     </row>
     <row r="133" spans="1:26" ht="21" customHeight="1">
-      <c r="A133" s="314"/>
-      <c r="B133" s="294" t="s">
+      <c r="A133" s="334"/>
+      <c r="B133" s="319" t="s">
         <v>225</v>
       </c>
-      <c r="C133" s="299" t="s">
+      <c r="C133" s="343" t="s">
         <v>226</v>
       </c>
       <c r="D133" s="104" t="s">
@@ -13914,9 +13683,9 @@
       </c>
     </row>
     <row r="134" spans="1:26" ht="21" customHeight="1">
-      <c r="A134" s="314"/>
-      <c r="B134" s="292"/>
-      <c r="C134" s="300"/>
+      <c r="A134" s="334"/>
+      <c r="B134" s="320"/>
+      <c r="C134" s="344"/>
       <c r="D134" s="105" t="s">
         <v>17</v>
       </c>
@@ -13967,9 +13736,9 @@
       <c r="Z134" s="25"/>
     </row>
     <row r="135" spans="1:26" ht="21" customHeight="1">
-      <c r="A135" s="314"/>
-      <c r="B135" s="292"/>
-      <c r="C135" s="299" t="s">
+      <c r="A135" s="334"/>
+      <c r="B135" s="320"/>
+      <c r="C135" s="343" t="s">
         <v>230</v>
       </c>
       <c r="D135" s="104" t="s">
@@ -14028,9 +13797,9 @@
       </c>
     </row>
     <row r="136" spans="1:26" ht="21" customHeight="1">
-      <c r="A136" s="314"/>
-      <c r="B136" s="293"/>
-      <c r="C136" s="300"/>
+      <c r="A136" s="334"/>
+      <c r="B136" s="337"/>
+      <c r="C136" s="344"/>
       <c r="D136" s="104" t="s">
         <v>17</v>
       </c>
@@ -14081,8 +13850,8 @@
       <c r="Z136" s="25"/>
     </row>
     <row r="137" spans="1:26" ht="13.2">
-      <c r="A137" s="314"/>
-      <c r="B137" s="294" t="s">
+      <c r="A137" s="334"/>
+      <c r="B137" s="319" t="s">
         <v>232</v>
       </c>
       <c r="C137" s="98" t="s">
@@ -14144,8 +13913,8 @@
       </c>
     </row>
     <row r="138" spans="1:26" ht="13.2">
-      <c r="A138" s="314"/>
-      <c r="B138" s="296"/>
+      <c r="A138" s="334"/>
+      <c r="B138" s="336"/>
       <c r="C138" s="98" t="s">
         <v>235</v>
       </c>
@@ -14202,7 +13971,7 @@
       </c>
     </row>
     <row r="139" spans="1:26" ht="13.2">
-      <c r="A139" s="315"/>
+      <c r="A139" s="335"/>
       <c r="B139" s="87"/>
       <c r="C139" s="98"/>
       <c r="D139" s="104"/>
@@ -14252,7 +14021,7 @@
       <c r="Z139" s="25"/>
     </row>
     <row r="140" spans="1:26" ht="13.2">
-      <c r="A140" s="311" t="s">
+      <c r="A140" s="332" t="s">
         <v>238</v>
       </c>
       <c r="B140" s="48" t="s">
@@ -14300,7 +14069,7 @@
       </c>
     </row>
     <row r="141" spans="1:26" ht="13.2">
-      <c r="A141" s="312"/>
+      <c r="A141" s="333"/>
       <c r="B141" s="48" t="s">
         <v>239</v>
       </c>
@@ -14346,7 +14115,7 @@
       </c>
     </row>
     <row r="142" spans="1:26" ht="26.4">
-      <c r="A142" s="312"/>
+      <c r="A142" s="333"/>
       <c r="B142" s="48" t="s">
         <v>244</v>
       </c>
@@ -14393,7 +14162,7 @@
       </c>
     </row>
     <row r="143" spans="1:26" ht="26.4">
-      <c r="A143" s="312"/>
+      <c r="A143" s="333"/>
       <c r="B143" s="48" t="s">
         <v>28</v>
       </c>
@@ -14439,7 +14208,7 @@
       </c>
     </row>
     <row r="144" spans="1:26" ht="39.6">
-      <c r="A144" s="312"/>
+      <c r="A144" s="333"/>
       <c r="B144" s="48" t="s">
         <v>26</v>
       </c>
@@ -14485,7 +14254,7 @@
       </c>
     </row>
     <row r="145" spans="1:26" ht="13.2">
-      <c r="A145" s="312"/>
+      <c r="A145" s="333"/>
       <c r="B145" s="48" t="s">
         <v>28</v>
       </c>
@@ -14523,7 +14292,7 @@
       </c>
     </row>
     <row r="146" spans="1:26" ht="26.4">
-      <c r="A146" s="297" t="s">
+      <c r="A146" s="353" t="s">
         <v>413</v>
       </c>
       <c r="B146" s="117" t="s">
@@ -14563,7 +14332,7 @@
       <c r="Z146" s="25"/>
     </row>
     <row r="147" spans="1:26" ht="13.2">
-      <c r="A147" s="297"/>
+      <c r="A147" s="353"/>
       <c r="B147" s="117"/>
       <c r="C147" s="196" t="s">
         <v>423</v>
@@ -14599,7 +14368,7 @@
       <c r="Z147" s="25"/>
     </row>
     <row r="148" spans="1:26" ht="26.4">
-      <c r="A148" s="297"/>
+      <c r="A148" s="353"/>
       <c r="B148" s="117"/>
       <c r="C148" s="98" t="s">
         <v>426</v>
@@ -14637,7 +14406,7 @@
       <c r="Z148" s="25"/>
     </row>
     <row r="149" spans="1:26" ht="13.2">
-      <c r="A149" s="297"/>
+      <c r="A149" s="353"/>
       <c r="B149" s="117"/>
       <c r="C149" s="98"/>
       <c r="D149" s="189"/>
@@ -14665,7 +14434,7 @@
       <c r="Z149" s="25"/>
     </row>
     <row r="150" spans="1:26" ht="13.2">
-      <c r="A150" s="297"/>
+      <c r="A150" s="353"/>
       <c r="B150" s="117" t="s">
         <v>416</v>
       </c>
@@ -14703,7 +14472,7 @@
       <c r="Z150" s="25"/>
     </row>
     <row r="151" spans="1:26" ht="13.2">
-      <c r="A151" s="297"/>
+      <c r="A151" s="353"/>
       <c r="B151" s="117"/>
       <c r="C151" s="183"/>
       <c r="D151" s="189"/>
@@ -14731,7 +14500,7 @@
       <c r="Z151" s="25"/>
     </row>
     <row r="152" spans="1:26" ht="13.2">
-      <c r="A152" s="297"/>
+      <c r="A152" s="353"/>
       <c r="B152" s="117"/>
       <c r="C152" s="183"/>
       <c r="D152" s="189"/>
@@ -14759,7 +14528,7 @@
       <c r="Z152" s="25"/>
     </row>
     <row r="153" spans="1:26" ht="26.4">
-      <c r="A153" s="297"/>
+      <c r="A153" s="353"/>
       <c r="B153" s="118" t="s">
         <v>252</v>
       </c>
@@ -14797,7 +14566,7 @@
       <c r="Z153" s="25"/>
     </row>
     <row r="154" spans="1:26" ht="26.4">
-      <c r="A154" s="297"/>
+      <c r="A154" s="353"/>
       <c r="B154" s="117"/>
       <c r="C154" s="196" t="s">
         <v>425</v>
@@ -14833,7 +14602,7 @@
       <c r="Z154" s="25"/>
     </row>
     <row r="155" spans="1:26" ht="13.2">
-      <c r="A155" s="297"/>
+      <c r="A155" s="353"/>
       <c r="B155" s="117"/>
       <c r="C155" s="196"/>
       <c r="D155" s="189"/>
@@ -14861,7 +14630,7 @@
       <c r="Z155" s="25"/>
     </row>
     <row r="156" spans="1:26" ht="13.2">
-      <c r="A156" s="297"/>
+      <c r="A156" s="353"/>
       <c r="B156" s="117"/>
       <c r="C156" s="196"/>
       <c r="D156" s="189"/>
@@ -14889,11 +14658,11 @@
       <c r="Z156" s="25"/>
     </row>
     <row r="157" spans="1:26" ht="13.2">
-      <c r="A157" s="297"/>
-      <c r="B157" s="298" t="s">
+      <c r="A157" s="353"/>
+      <c r="B157" s="354" t="s">
         <v>253</v>
       </c>
-      <c r="C157" s="332" t="s">
+      <c r="C157" s="324" t="s">
         <v>418</v>
       </c>
       <c r="D157" s="189" t="s">
@@ -14923,9 +14692,9 @@
       <c r="Z157" s="25"/>
     </row>
     <row r="158" spans="1:26" ht="13.2">
-      <c r="A158" s="297"/>
-      <c r="B158" s="298"/>
-      <c r="C158" s="333"/>
+      <c r="A158" s="353"/>
+      <c r="B158" s="354"/>
+      <c r="C158" s="325"/>
       <c r="D158" s="189"/>
       <c r="E158" s="104"/>
       <c r="F158" s="213"/>
@@ -14951,9 +14720,9 @@
       <c r="Z158" s="25"/>
     </row>
     <row r="159" spans="1:26" ht="13.2">
-      <c r="A159" s="297"/>
-      <c r="B159" s="298"/>
-      <c r="C159" s="332" t="s">
+      <c r="A159" s="353"/>
+      <c r="B159" s="354"/>
+      <c r="C159" s="324" t="s">
         <v>432</v>
       </c>
       <c r="D159" s="189" t="s">
@@ -14985,9 +14754,9 @@
       <c r="Z159" s="25"/>
     </row>
     <row r="160" spans="1:26" ht="13.2">
-      <c r="A160" s="297"/>
-      <c r="B160" s="298"/>
-      <c r="C160" s="333"/>
+      <c r="A160" s="353"/>
+      <c r="B160" s="354"/>
+      <c r="C160" s="325"/>
       <c r="D160" s="189"/>
       <c r="E160" s="104"/>
       <c r="F160" s="213"/>
@@ -15013,9 +14782,9 @@
       <c r="Z160" s="25"/>
     </row>
     <row r="161" spans="1:26" ht="13.2">
-      <c r="A161" s="297"/>
-      <c r="B161" s="298"/>
-      <c r="C161" s="332" t="s">
+      <c r="A161" s="353"/>
+      <c r="B161" s="354"/>
+      <c r="C161" s="324" t="s">
         <v>434</v>
       </c>
       <c r="D161" s="189" t="s">
@@ -15047,9 +14816,9 @@
       <c r="Z161" s="25"/>
     </row>
     <row r="162" spans="1:26" ht="13.2">
-      <c r="A162" s="297"/>
-      <c r="B162" s="298"/>
-      <c r="C162" s="333"/>
+      <c r="A162" s="353"/>
+      <c r="B162" s="354"/>
+      <c r="C162" s="325"/>
       <c r="D162" s="189"/>
       <c r="E162" s="104"/>
       <c r="F162" s="213"/>
@@ -15075,8 +14844,8 @@
       <c r="Z162" s="25"/>
     </row>
     <row r="163" spans="1:26" ht="13.2">
-      <c r="A163" s="297"/>
-      <c r="B163" s="298"/>
+      <c r="A163" s="353"/>
+      <c r="B163" s="354"/>
       <c r="C163" s="117" t="s">
         <v>435</v>
       </c>
@@ -15109,8 +14878,8 @@
       <c r="Z163" s="25"/>
     </row>
     <row r="164" spans="1:26" ht="13.2">
-      <c r="A164" s="297"/>
-      <c r="B164" s="298"/>
+      <c r="A164" s="353"/>
+      <c r="B164" s="354"/>
       <c r="C164" s="117"/>
       <c r="D164" s="189"/>
       <c r="E164" s="104"/>
@@ -15137,8 +14906,8 @@
       <c r="Z164" s="25"/>
     </row>
     <row r="165" spans="1:26" ht="13.2">
-      <c r="A165" s="297"/>
-      <c r="B165" s="298"/>
+      <c r="A165" s="353"/>
+      <c r="B165" s="354"/>
       <c r="C165" s="117" t="s">
         <v>436</v>
       </c>
@@ -15171,8 +14940,8 @@
       <c r="Z165" s="25"/>
     </row>
     <row r="166" spans="1:26" ht="13.2">
-      <c r="A166" s="297"/>
-      <c r="B166" s="298"/>
+      <c r="A166" s="353"/>
+      <c r="B166" s="354"/>
       <c r="C166" s="117"/>
       <c r="D166" s="189"/>
       <c r="E166" s="104"/>
@@ -15199,8 +14968,8 @@
       <c r="Z166" s="25"/>
     </row>
     <row r="167" spans="1:26" ht="13.2">
-      <c r="A167" s="297"/>
-      <c r="B167" s="298"/>
+      <c r="A167" s="353"/>
+      <c r="B167" s="354"/>
       <c r="C167" s="117" t="s">
         <v>437</v>
       </c>
@@ -15233,8 +15002,8 @@
       <c r="Z167" s="25"/>
     </row>
     <row r="168" spans="1:26" ht="13.2">
-      <c r="A168" s="297"/>
-      <c r="B168" s="298"/>
+      <c r="A168" s="353"/>
+      <c r="B168" s="354"/>
       <c r="C168" s="117"/>
       <c r="D168" s="189"/>
       <c r="E168" s="104"/>
@@ -15261,8 +15030,8 @@
       <c r="Z168" s="25"/>
     </row>
     <row r="169" spans="1:26" ht="13.2">
-      <c r="A169" s="297"/>
-      <c r="B169" s="298"/>
+      <c r="A169" s="353"/>
+      <c r="B169" s="354"/>
       <c r="C169" s="117" t="s">
         <v>438</v>
       </c>
@@ -15295,8 +15064,8 @@
       <c r="Z169" s="25"/>
     </row>
     <row r="170" spans="1:26" ht="13.2">
-      <c r="A170" s="297"/>
-      <c r="B170" s="298"/>
+      <c r="A170" s="353"/>
+      <c r="B170" s="354"/>
       <c r="C170" s="200"/>
       <c r="D170" s="189"/>
       <c r="E170" s="104"/>
@@ -15323,9 +15092,9 @@
       <c r="Z170" s="25"/>
     </row>
     <row r="171" spans="1:26" ht="13.2">
-      <c r="A171" s="297"/>
-      <c r="B171" s="298"/>
-      <c r="C171" s="332" t="s">
+      <c r="A171" s="353"/>
+      <c r="B171" s="354"/>
+      <c r="C171" s="324" t="s">
         <v>439</v>
       </c>
       <c r="D171" s="189" t="s">
@@ -15357,9 +15126,9 @@
       <c r="Z171" s="25"/>
     </row>
     <row r="172" spans="1:26" ht="13.2">
-      <c r="A172" s="297"/>
-      <c r="B172" s="298"/>
-      <c r="C172" s="333"/>
+      <c r="A172" s="353"/>
+      <c r="B172" s="354"/>
+      <c r="C172" s="325"/>
       <c r="D172" s="189" t="s">
         <v>17</v>
       </c>
@@ -15387,9 +15156,9 @@
       <c r="Z172" s="25"/>
     </row>
     <row r="173" spans="1:26" ht="13.2">
-      <c r="A173" s="297"/>
-      <c r="B173" s="298"/>
-      <c r="C173" s="332" t="s">
+      <c r="A173" s="353"/>
+      <c r="B173" s="354"/>
+      <c r="C173" s="324" t="s">
         <v>440</v>
       </c>
       <c r="D173" s="189" t="s">
@@ -15421,9 +15190,9 @@
       <c r="Z173" s="25"/>
     </row>
     <row r="174" spans="1:26" ht="13.2">
-      <c r="A174" s="297"/>
-      <c r="B174" s="298"/>
-      <c r="C174" s="333"/>
+      <c r="A174" s="353"/>
+      <c r="B174" s="354"/>
+      <c r="C174" s="325"/>
       <c r="D174" s="189" t="s">
         <v>17</v>
       </c>
@@ -15453,9 +15222,9 @@
       <c r="Z174" s="25"/>
     </row>
     <row r="175" spans="1:26" ht="13.2">
-      <c r="A175" s="297"/>
-      <c r="B175" s="298"/>
-      <c r="C175" s="330" t="s">
+      <c r="A175" s="353"/>
+      <c r="B175" s="354"/>
+      <c r="C175" s="322" t="s">
         <v>441</v>
       </c>
       <c r="D175" s="189" t="s">
@@ -15487,9 +15256,9 @@
       <c r="Z175" s="25"/>
     </row>
     <row r="176" spans="1:26" ht="13.2">
-      <c r="A176" s="297"/>
-      <c r="B176" s="298"/>
-      <c r="C176" s="331"/>
+      <c r="A176" s="353"/>
+      <c r="B176" s="354"/>
+      <c r="C176" s="323"/>
       <c r="D176" s="189" t="s">
         <v>17</v>
       </c>
@@ -15519,10 +15288,10 @@
       <c r="Z176" s="25"/>
     </row>
     <row r="177" spans="1:26" ht="13.2">
-      <c r="A177" s="290" t="s">
+      <c r="A177" s="328" t="s">
         <v>254</v>
       </c>
-      <c r="B177" s="292" t="s">
+      <c r="B177" s="320" t="s">
         <v>255</v>
       </c>
       <c r="C177" s="115" t="s">
@@ -15563,8 +15332,8 @@
       </c>
     </row>
     <row r="178" spans="1:26" ht="25.5" customHeight="1">
-      <c r="A178" s="290"/>
-      <c r="B178" s="293"/>
+      <c r="A178" s="328"/>
+      <c r="B178" s="337"/>
       <c r="C178" s="98" t="s">
         <v>256</v>
       </c>
@@ -15604,8 +15373,8 @@
       </c>
     </row>
     <row r="179" spans="1:26" ht="13.2">
-      <c r="A179" s="290"/>
-      <c r="B179" s="294" t="s">
+      <c r="A179" s="328"/>
+      <c r="B179" s="319" t="s">
         <v>259</v>
       </c>
       <c r="C179" s="98" t="s">
@@ -15667,9 +15436,9 @@
       </c>
     </row>
     <row r="180" spans="1:26" ht="13.2">
-      <c r="A180" s="290"/>
-      <c r="B180" s="292"/>
-      <c r="C180" s="305" t="s">
+      <c r="A180" s="328"/>
+      <c r="B180" s="320"/>
+      <c r="C180" s="317" t="s">
         <v>263</v>
       </c>
       <c r="D180" s="189" t="s">
@@ -15731,9 +15500,9 @@
       </c>
     </row>
     <row r="181" spans="1:26" ht="13.2">
-      <c r="A181" s="290"/>
-      <c r="B181" s="292"/>
-      <c r="C181" s="307"/>
+      <c r="A181" s="328"/>
+      <c r="B181" s="320"/>
+      <c r="C181" s="318"/>
       <c r="D181" s="189" t="s">
         <v>17</v>
       </c>
@@ -15791,8 +15560,8 @@
       </c>
     </row>
     <row r="182" spans="1:26" ht="13.2">
-      <c r="A182" s="290"/>
-      <c r="B182" s="292"/>
+      <c r="A182" s="328"/>
+      <c r="B182" s="320"/>
       <c r="C182" s="98" t="s">
         <v>265</v>
       </c>
@@ -15848,8 +15617,8 @@
       </c>
     </row>
     <row r="183" spans="1:26" ht="13.2">
-      <c r="A183" s="290"/>
-      <c r="B183" s="292"/>
+      <c r="A183" s="328"/>
+      <c r="B183" s="320"/>
       <c r="C183" s="61" t="s">
         <v>266</v>
       </c>
@@ -15903,8 +15672,8 @@
       </c>
     </row>
     <row r="184" spans="1:26" ht="13.2">
-      <c r="A184" s="290"/>
-      <c r="B184" s="292"/>
+      <c r="A184" s="328"/>
+      <c r="B184" s="320"/>
       <c r="C184" s="61" t="s">
         <v>267</v>
       </c>
@@ -15938,8 +15707,8 @@
       </c>
     </row>
     <row r="185" spans="1:26" ht="13.2">
-      <c r="A185" s="290"/>
-      <c r="B185" s="292"/>
+      <c r="A185" s="328"/>
+      <c r="B185" s="320"/>
       <c r="C185" s="61" t="s">
         <v>268</v>
       </c>
@@ -15973,8 +15742,8 @@
       </c>
     </row>
     <row r="186" spans="1:26" ht="13.2">
-      <c r="A186" s="290"/>
-      <c r="B186" s="293"/>
+      <c r="A186" s="328"/>
+      <c r="B186" s="337"/>
       <c r="C186" s="61" t="s">
         <v>269</v>
       </c>
@@ -16008,8 +15777,8 @@
       </c>
     </row>
     <row r="187" spans="1:26" ht="13.2">
-      <c r="A187" s="290"/>
-      <c r="B187" s="294" t="s">
+      <c r="A187" s="328"/>
+      <c r="B187" s="319" t="s">
         <v>270</v>
       </c>
       <c r="C187" s="98" t="s">
@@ -16075,8 +15844,8 @@
       </c>
     </row>
     <row r="188" spans="1:26" ht="26.4">
-      <c r="A188" s="290"/>
-      <c r="B188" s="295"/>
+      <c r="A188" s="328"/>
+      <c r="B188" s="338"/>
       <c r="C188" s="98" t="s">
         <v>272</v>
       </c>
@@ -16115,8 +15884,8 @@
       </c>
     </row>
     <row r="189" spans="1:26" ht="13.2">
-      <c r="A189" s="290"/>
-      <c r="B189" s="295"/>
+      <c r="A189" s="328"/>
+      <c r="B189" s="338"/>
       <c r="C189" s="98" t="s">
         <v>273</v>
       </c>
@@ -16155,8 +15924,8 @@
       </c>
     </row>
     <row r="190" spans="1:26" ht="13.2">
-      <c r="A190" s="290"/>
-      <c r="B190" s="296"/>
+      <c r="A190" s="328"/>
+      <c r="B190" s="336"/>
       <c r="C190" s="98" t="s">
         <v>274</v>
       </c>
@@ -16193,7 +15962,7 @@
       <c r="Z190" s="25"/>
     </row>
     <row r="191" spans="1:26" ht="13.2">
-      <c r="A191" s="291"/>
+      <c r="A191" s="297"/>
       <c r="B191" s="26" t="s">
         <v>276</v>
       </c>
@@ -16305,6 +16074,81 @@
     </row>
   </sheetData>
   <mergeCells count="91">
+    <mergeCell ref="A177:A191"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="B187:B190"/>
+    <mergeCell ref="B179:B186"/>
+    <mergeCell ref="A146:A176"/>
+    <mergeCell ref="B157:B176"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="C124:C127"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="C98:C100"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="C110:C112"/>
+    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="A140:A145"/>
+    <mergeCell ref="A121:A139"/>
+    <mergeCell ref="A98:A120"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="B133:B136"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="B121:B127"/>
+    <mergeCell ref="B128:B132"/>
+    <mergeCell ref="B110:B120"/>
+    <mergeCell ref="W31:W37"/>
+    <mergeCell ref="A3:A45"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B8:B16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B39"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="B21:B25"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C180:C181"/>
+    <mergeCell ref="C175:C176"/>
+    <mergeCell ref="C173:C174"/>
+    <mergeCell ref="C171:C172"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="C159:C160"/>
+    <mergeCell ref="C161:C162"/>
+    <mergeCell ref="B61:B70"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="B74:B83"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="B84:B93"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="B102:B109"/>
+    <mergeCell ref="B94:B96"/>
+    <mergeCell ref="D81:D83"/>
+    <mergeCell ref="C81:C83"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="D63:D67"/>
+    <mergeCell ref="C63:C67"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
     <mergeCell ref="A46:A96"/>
     <mergeCell ref="C56:C57"/>
     <mergeCell ref="D56:D57"/>
@@ -16321,200 +16165,171 @@
     <mergeCell ref="D88:D89"/>
     <mergeCell ref="D91:D92"/>
     <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="D81:D83"/>
-    <mergeCell ref="C81:C83"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="D63:D67"/>
-    <mergeCell ref="C63:C67"/>
-    <mergeCell ref="D68:D70"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="B61:B70"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="B74:B83"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="B71:B73"/>
-    <mergeCell ref="B84:B93"/>
-    <mergeCell ref="C84:C86"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="B102:B109"/>
-    <mergeCell ref="B94:B96"/>
-    <mergeCell ref="C180:C181"/>
-    <mergeCell ref="C175:C176"/>
-    <mergeCell ref="C173:C174"/>
-    <mergeCell ref="C171:C172"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="C159:C160"/>
-    <mergeCell ref="C161:C162"/>
-    <mergeCell ref="W31:W37"/>
-    <mergeCell ref="A3:A45"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B8:B16"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B39"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="B21:B25"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="A140:A145"/>
-    <mergeCell ref="A121:A139"/>
-    <mergeCell ref="A98:A120"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="B133:B136"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="B121:B127"/>
-    <mergeCell ref="B128:B132"/>
-    <mergeCell ref="B110:B120"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="C124:C127"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="C98:C100"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="C110:C112"/>
-    <mergeCell ref="C113:C115"/>
-    <mergeCell ref="A177:A191"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="B187:B190"/>
-    <mergeCell ref="B179:B186"/>
-    <mergeCell ref="A146:A176"/>
-    <mergeCell ref="B157:B176"/>
   </mergeCells>
   <phoneticPr fontId="36" type="noConversion"/>
+  <conditionalFormatting sqref="D43 E43:E44">
+    <cfRule type="containsText" dxfId="101" priority="1" operator="containsText" text="Ja">
+      <formula>NOT(ISERROR(SEARCH(("Ja"),(D43))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="100" priority="2" operator="containsText" text="Nee">
+      <formula>NOT(ISERROR(SEARCH(("Nee"),(D43))))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="3" operator="equal">
+      <formula>"Via andere grondstof"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="98" priority="4" operator="equal">
+      <formula>"Oppervlakkig"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D1:E2 D98:E193">
-    <cfRule type="cellIs" dxfId="131" priority="103" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="103" operator="equal">
       <formula>"Voorbeeld"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:E18 E19 D20:E32 E33 D34:E37 E38:E39 D40:E42 E47 D48:E52 E53 D54:E54 E55 D56:E56 E57:E59 D60:E61 E62 D63:E63 E64:E67 D68:E68 E69:E70 D71:E76 E77:E78 D79:E79 E80 D81:E81 E82:E83 D84:E84 E85:E86 D87:E88 E89 D90:E91 E92 D93:E97 D45:E46">
-    <cfRule type="containsText" dxfId="130" priority="96" operator="containsText" text="Ja">
+  <conditionalFormatting sqref="D3:E18 E19 D20:E32 E33 D34:E37 E38:E39 D40:E42 D45:E46 E47 D48:E52 E53 D54:E54 E55 D56:E56 E57:E59 D60:E61 E62 D63:E63 E64:E67 D68:E68 E69:E70 D71:E76 E77:E78 D79:E79 E80 D81:E81 E82:E83 D84:E84 E85:E86 D87:E88 E89 D90:E91 E92 D93:E97">
+    <cfRule type="containsText" dxfId="96" priority="96" operator="containsText" text="Ja">
       <formula>NOT(ISERROR(SEARCH(("Ja"),(D3))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="129" priority="97" operator="containsText" text="Nee">
+    <cfRule type="cellIs" dxfId="95" priority="99" operator="equal">
+      <formula>"Oppervlakkig"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="98" operator="equal">
+      <formula>"Via andere grondstof"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="93" priority="97" operator="containsText" text="Nee">
       <formula>NOT(ISERROR(SEARCH(("Nee"),(D3))))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="98" operator="equal">
-      <formula>"Via andere grondstof"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:P2 F3:P21 F22 I22:P22 F23:P31 F32:F33 I32:P33 F34:P34 F35:F37 I35:P38 F39:P39 F39:F40 I40:P40 F41:P41 H42:P42 F45:P45 H46:P60 F46:F89 I61:P67 I69:P97 F91:F97 D98:P109 D110:F115 I110:P115">
+    <cfRule type="containsText" dxfId="92" priority="120" operator="containsText" text="Nee">
+      <formula>NOT(ISERROR(SEARCH(("Nee"),(D1))))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="99" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="130" operator="equal">
       <formula>"Oppervlakkig"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:P2 F3:P21 F22 I22:P22 F23:P31 F32:F33 I32:P33 F34:P34 F35:F37 I35:P38 F39:P39 F39:F40 I40:P40 F41:P41 F42 H42:P42 F45:P45 H46:P60 F46:F89 I61:P67 I69:P97 F91:F97 D98:P109 D110:F115 I110:P115">
-    <cfRule type="cellIs" dxfId="126" priority="127" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="127" operator="equal">
       <formula>"Via andere grondstof"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="130" operator="equal">
-      <formula>"Oppervlakkig"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:P2 Z2:Z42 F3:P21 F22 I22:P22 F23:P31 F32:F33 I32:P33 F34:P34 F35:F37 I35:P38 F39:P39 F39:F40 I40:P40 F41:P41 F42 H42:P42 F45:P45 H46:P60 F46:F89 I61:P67 I69:P97 F91:F97 D98:P109 D110:F115 I110:P115 Z45:Z193">
-    <cfRule type="containsText" dxfId="124" priority="120" operator="containsText" text="Nee">
-      <formula>NOT(ISERROR(SEARCH(("Nee"),(D1))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:P124 D125:F127 D128:P139 D140:H145 D146:P158 D159:F176 D177:P178 D179:F186 D187:P193 I125:P127 I159:P176 I179:P186">
-    <cfRule type="containsText" dxfId="123" priority="106" operator="containsText" text="Ja">
+    <cfRule type="containsText" dxfId="89" priority="106" operator="containsText" text="Ja">
       <formula>NOT(ISERROR(SEARCH(("Ja"),(D116))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D116:P124 D125:F127 I125:P127 D128:P139 D140:H145 D146:P158 D159:F176 I159:P176 D177:P178 D179:F186 I179:P186 D187:P193">
-    <cfRule type="containsText" dxfId="122" priority="107" operator="containsText" text="Nee">
+    <cfRule type="cellIs" dxfId="88" priority="109" operator="equal">
+      <formula>"Oppervlakkig"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="87" priority="107" operator="containsText" text="Nee">
       <formula>NOT(ISERROR(SEARCH(("Nee"),(D116))))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="108" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="108" operator="equal">
       <formula>"Via andere grondstof"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="109" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F37 F39:F42 F45:F89 F91:F131 G122:H123 F132:H132 F133:F193 C145:C152 B153 C154:C157 C159">
+    <cfRule type="cellIs" dxfId="85" priority="125" operator="equal">
+      <formula>"nvt"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F42:F43 H43:P44">
+    <cfRule type="cellIs" dxfId="84" priority="23" operator="equal">
+      <formula>"Via andere grondstof"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="83" priority="26" operator="equal">
       <formula>"Oppervlakkig"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F37 F39:F42 F91:F131 G122:H123 F132:H132 F133:F193 C145:C152 B153 C154:C157 C159 F45:F89">
-    <cfRule type="cellIs" dxfId="119" priority="125" operator="equal">
+  <conditionalFormatting sqref="F42:F43">
+    <cfRule type="containsText" dxfId="82" priority="13" operator="containsText" text="Ja">
+      <formula>NOT(ISERROR(SEARCH(("Ja"),(F42))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F43">
+    <cfRule type="cellIs" dxfId="81" priority="12" operator="equal">
+      <formula>"Betrouwbaar"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="80" priority="21" operator="equal">
       <formula>"nvt"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107:H109 F110:F115 F116:H124 F125:F126 F128:H158 R146:R193 F159:F176 F177:H178 F179:F186 F187:H193">
-    <cfRule type="cellIs" dxfId="118" priority="105" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="105" operator="equal">
       <formula>"Betrouwbaar"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23:P31 F34:P34 F39:P39 F41:P41 H42:P42 F45:P45 H46:P60 D98:P109 D110:F115 D1:P2 F3:P21 I22:P22 I32:P33 I35:P38 I40:P40 I61:P67 I69:P97 I110:P115 Z2:Z42 F22 F32:F33 F35:F37 F39:F40 F42 F46:F89 F91:F97 Z45:Z193">
-    <cfRule type="containsText" dxfId="117" priority="119" operator="containsText" text="Ja">
+  <conditionalFormatting sqref="F23:P31 F34:P34 F39:P39 F41:P41 F45:P45 H46:P60 D98:P109 D110:F115 D1:P2 F3:P21 I22:P22 I32:P33 I35:P38 I40:P40 H42:P42 I61:P67 I69:P97 I110:P115 F22 F32:F33 F35:F37 F39:F40 F46:F89 F91:F97">
+    <cfRule type="containsText" dxfId="78" priority="119" operator="containsText" text="Ja">
       <formula>NOT(ISERROR(SEARCH(("Ja"),(D1))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:H21 F4:F16 F20 F23:F25 F27:F28 F30:F37 F39:F42 F91:F96 F98:H106 F127 R1:R42 C145:C152 B153 C154:C157 C159 R45:R139 F45:F89">
-    <cfRule type="cellIs" dxfId="116" priority="121" operator="equal">
+  <conditionalFormatting sqref="G1:H21 F4:F16 F20 F23:F25 F27:F28 F30:F37 F39:F42 F45:F89 F91:F96 F98:H106 F127 C145:C152 B153 C154:C157 C159">
+    <cfRule type="cellIs" dxfId="77" priority="121" operator="equal">
       <formula>"Betrouwbaar"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:H31 G34:H34 G39:H39 G41:H41 H42 G45:H45 H46:H60 F104">
-    <cfRule type="cellIs" dxfId="115" priority="115" operator="equal">
+  <conditionalFormatting sqref="G23:H31 G34:H34 G39:H39 G41:H41 G45:H45 H46:H60 F104">
+    <cfRule type="cellIs" dxfId="76" priority="115" operator="equal">
       <formula>"Betrouwbaar"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G110:H112">
-    <cfRule type="cellIs" dxfId="114" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="46" operator="equal">
       <formula>"Betrouwbaar"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G111:H112">
-    <cfRule type="containsText" dxfId="113" priority="42" operator="containsText" text="Ja">
-      <formula>NOT(ISERROR(SEARCH(("Ja"),(G111))))</formula>
+    <cfRule type="cellIs" dxfId="74" priority="45" operator="equal">
+      <formula>"Oppervlakkig"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="112" priority="43" operator="containsText" text="Nee">
+    <cfRule type="containsText" dxfId="73" priority="43" operator="containsText" text="Nee">
       <formula>NOT(ISERROR(SEARCH(("Nee"),(G111))))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="44" operator="equal">
       <formula>"Via andere grondstof"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="45" operator="equal">
-      <formula>"Oppervlakkig"</formula>
+    <cfRule type="containsText" dxfId="71" priority="42" operator="containsText" text="Ja">
+      <formula>NOT(ISERROR(SEARCH(("Ja"),(G111))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G111:H115">
-    <cfRule type="cellIs" dxfId="109" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="29" operator="equal">
       <formula>"Betrouwbaar"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G114:H115">
-    <cfRule type="containsText" dxfId="108" priority="30" operator="containsText" text="Ja">
+    <cfRule type="containsText" dxfId="69" priority="30" operator="containsText" text="Ja">
       <formula>NOT(ISERROR(SEARCH(("Ja"),(G114))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="107" priority="31" operator="containsText" text="Nee">
+    <cfRule type="containsText" dxfId="68" priority="31" operator="containsText" text="Nee">
       <formula>NOT(ISERROR(SEARCH(("Nee"),(G114))))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="32" operator="equal">
       <formula>"Via andere grondstof"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="33" operator="equal">
       <formula>"Oppervlakkig"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G114:H120">
-    <cfRule type="cellIs" dxfId="104" priority="100" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="100" operator="equal">
       <formula>"Betrouwbaar"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H42:H44 R1:R139">
+    <cfRule type="cellIs" dxfId="64" priority="17" operator="equal">
+      <formula>"Betrouwbaar"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H43:P44 Z2:Z193">
+    <cfRule type="containsText" dxfId="63" priority="15" operator="containsText" text="Ja">
+      <formula>NOT(ISERROR(SEARCH(("Ja"),(H2))))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I68">
+    <cfRule type="containsText" dxfId="62" priority="93" operator="containsText" text="Nee">
+      <formula>NOT(ISERROR(SEARCH(("Nee"),(I68))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -16525,22 +16340,31 @@
         <color theme="5"/>
       </colorScale>
     </cfRule>
-    <cfRule type="containsText" dxfId="103" priority="92" operator="containsText" text="Ja">
+    <cfRule type="containsText" dxfId="61" priority="92" operator="containsText" text="Ja">
       <formula>NOT(ISERROR(SEARCH(("Ja"),(I68))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="102" priority="93" operator="containsText" text="Nee">
-      <formula>NOT(ISERROR(SEARCH(("Nee"),(I68))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="94" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="94" operator="equal">
       <formula>"Via andere grondstof"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="95" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="95" operator="equal">
       <formula>"Oppervlakkig"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:P42 I45:P139">
-    <cfRule type="cellIs" dxfId="99" priority="48" operator="equal">
+  <conditionalFormatting sqref="I1:P139">
+    <cfRule type="cellIs" dxfId="58" priority="6" operator="equal">
       <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I43:P44">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="3"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="FF00B050"/>
+        <color rgb="FFFFEB84"/>
+        <color theme="5"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I146:P193 I69:P139 I1:P42 I45:P67">
@@ -16556,11 +16380,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I146:P193">
-    <cfRule type="cellIs" dxfId="98" priority="102" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="102" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I140:R145">
+    <cfRule type="cellIs" dxfId="56" priority="122" operator="equal">
+      <formula>"Nee"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J68">
+    <cfRule type="containsText" dxfId="55" priority="86" operator="containsText" text="Ja">
+      <formula>NOT(ISERROR(SEARCH(("Ja"),(J68))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="54" priority="87" operator="containsText" text="Nee">
+      <formula>NOT(ISERROR(SEARCH(("Nee"),(J68))))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="88" operator="equal">
+      <formula>"Via andere grondstof"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="89" operator="equal">
+      <formula>"Oppervlakkig"</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="85">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -16570,18 +16411,6 @@
         <color rgb="FFFFEB84"/>
         <color theme="5"/>
       </colorScale>
-    </cfRule>
-    <cfRule type="containsText" dxfId="97" priority="86" operator="containsText" text="Ja">
-      <formula>NOT(ISERROR(SEARCH(("Ja"),(J68))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="96" priority="87" operator="containsText" text="Nee">
-      <formula>NOT(ISERROR(SEARCH(("Nee"),(J68))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="88" operator="equal">
-      <formula>"Via andere grondstof"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="89" operator="equal">
-      <formula>"Oppervlakkig"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K68">
@@ -16595,20 +16424,32 @@
         <color theme="5"/>
       </colorScale>
     </cfRule>
-    <cfRule type="containsText" dxfId="93" priority="80" operator="containsText" text="Ja">
+    <cfRule type="containsText" dxfId="51" priority="81" operator="containsText" text="Nee">
+      <formula>NOT(ISERROR(SEARCH(("Nee"),(K68))))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="50" priority="82" operator="equal">
+      <formula>"Via andere grondstof"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="49" priority="80" operator="containsText" text="Ja">
       <formula>NOT(ISERROR(SEARCH(("Ja"),(K68))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="92" priority="81" operator="containsText" text="Nee">
-      <formula>NOT(ISERROR(SEARCH(("Nee"),(K68))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="82" operator="equal">
-      <formula>"Via andere grondstof"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="83" operator="equal">
       <formula>"Oppervlakkig"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L68">
+    <cfRule type="cellIs" dxfId="47" priority="77" operator="equal">
+      <formula>"Oppervlakkig"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="76" operator="equal">
+      <formula>"Via andere grondstof"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="45" priority="75" operator="containsText" text="Nee">
+      <formula>NOT(ISERROR(SEARCH(("Nee"),(L68))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="44" priority="74" operator="containsText" text="Ja">
+      <formula>NOT(ISERROR(SEARCH(("Ja"),(L68))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="73">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -16619,20 +16460,20 @@
         <color theme="5"/>
       </colorScale>
     </cfRule>
-    <cfRule type="containsText" dxfId="89" priority="74" operator="containsText" text="Ja">
-      <formula>NOT(ISERROR(SEARCH(("Ja"),(L68))))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M68">
+    <cfRule type="cellIs" dxfId="43" priority="71" operator="equal">
+      <formula>"Oppervlakkig"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="75" operator="containsText" text="Nee">
-      <formula>NOT(ISERROR(SEARCH(("Nee"),(L68))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="70" operator="equal">
       <formula>"Via andere grondstof"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="77" operator="equal">
-      <formula>"Oppervlakkig"</formula>
+    <cfRule type="containsText" dxfId="41" priority="69" operator="containsText" text="Nee">
+      <formula>NOT(ISERROR(SEARCH(("Nee"),(M68))))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M68">
+    <cfRule type="containsText" dxfId="40" priority="68" operator="containsText" text="Ja">
+      <formula>NOT(ISERROR(SEARCH(("Ja"),(M68))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="67">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -16643,20 +16484,11 @@
         <color theme="5"/>
       </colorScale>
     </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="68" operator="containsText" text="Ja">
-      <formula>NOT(ISERROR(SEARCH(("Ja"),(M68))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="69" operator="containsText" text="Nee">
-      <formula>NOT(ISERROR(SEARCH(("Nee"),(M68))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="70" operator="equal">
-      <formula>"Via andere grondstof"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="71" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N68">
+    <cfRule type="cellIs" dxfId="39" priority="65" operator="equal">
       <formula>"Oppervlakkig"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N68">
     <cfRule type="colorScale" priority="61">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -16667,20 +16499,26 @@
         <color theme="5"/>
       </colorScale>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="62" operator="containsText" text="Ja">
+    <cfRule type="containsText" dxfId="38" priority="62" operator="containsText" text="Ja">
       <formula>NOT(ISERROR(SEARCH(("Ja"),(N68))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="80" priority="63" operator="containsText" text="Nee">
+    <cfRule type="containsText" dxfId="37" priority="63" operator="containsText" text="Nee">
       <formula>NOT(ISERROR(SEARCH(("Nee"),(N68))))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="64" operator="equal">
       <formula>"Via andere grondstof"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="65" operator="equal">
-      <formula>"Oppervlakkig"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O68">
+    <cfRule type="cellIs" dxfId="35" priority="53" operator="equal">
+      <formula>"Oppervlakkig"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="52" operator="equal">
+      <formula>"Via andere grondstof"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="33" priority="51" operator="containsText" text="Nee">
+      <formula>NOT(ISERROR(SEARCH(("Nee"),(O68))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -16691,20 +16529,23 @@
         <color theme="5"/>
       </colorScale>
     </cfRule>
-    <cfRule type="containsText" dxfId="77" priority="50" operator="containsText" text="Ja">
+    <cfRule type="containsText" dxfId="32" priority="50" operator="containsText" text="Ja">
       <formula>NOT(ISERROR(SEARCH(("Ja"),(O68))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="51" operator="containsText" text="Nee">
-      <formula>NOT(ISERROR(SEARCH(("Nee"),(O68))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="52" operator="equal">
-      <formula>"Via andere grondstof"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="53" operator="equal">
-      <formula>"Oppervlakkig"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P68">
+    <cfRule type="cellIs" dxfId="31" priority="59" operator="equal">
+      <formula>"Oppervlakkig"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="58" operator="equal">
+      <formula>"Via andere grondstof"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="29" priority="57" operator="containsText" text="Nee">
+      <formula>NOT(ISERROR(SEARCH(("Nee"),(P68))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="28" priority="56" operator="containsText" text="Ja">
+      <formula>NOT(ISERROR(SEARCH(("Ja"),(P68))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -16715,184 +16556,60 @@
         <color theme="5"/>
       </colorScale>
     </cfRule>
-    <cfRule type="containsText" dxfId="73" priority="56" operator="containsText" text="Ja">
-      <formula>NOT(ISERROR(SEARCH(("Ja"),(P68))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="57" operator="containsText" text="Nee">
-      <formula>NOT(ISERROR(SEARCH(("Nee"),(P68))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="58" operator="equal">
-      <formula>"Via andere grondstof"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="59" operator="equal">
-      <formula>"Oppervlakkig"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q42 Q45:Q1048576">
-    <cfRule type="cellIs" dxfId="69" priority="47" operator="greaterThan">
+  <conditionalFormatting sqref="Q2:Q1048576">
+    <cfRule type="cellIs" dxfId="27" priority="5" operator="greaterThan">
       <formula>2.4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S1:S42 T2:T42 I140:R145 S45:T193">
-    <cfRule type="cellIs" dxfId="68" priority="123" operator="equal">
+  <conditionalFormatting sqref="S1:S42 T2:T42 I140:R145">
+    <cfRule type="cellIs" dxfId="26" priority="123" operator="equal">
       <formula>"mogelijk"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="124" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="124" operator="equal">
       <formula>"Ja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S1:S42 I140:R145 S45:S193">
-    <cfRule type="cellIs" dxfId="66" priority="122" operator="equal">
+  <conditionalFormatting sqref="S1:S193">
+    <cfRule type="cellIs" dxfId="24" priority="18" operator="equal">
       <formula>"Nee"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T1:T42 T45:T193">
-    <cfRule type="cellIs" dxfId="65" priority="126" operator="equal">
+  <conditionalFormatting sqref="S43:T193">
+    <cfRule type="cellIs" dxfId="23" priority="20" operator="equal">
+      <formula>"Ja"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="19" operator="equal">
+      <formula>"mogelijk"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T1:T193">
+    <cfRule type="cellIs" dxfId="21" priority="22" operator="equal">
       <formula>"nvt"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T42 T45:T193">
-    <cfRule type="cellIs" dxfId="64" priority="131" operator="equal">
+  <conditionalFormatting sqref="T2:T193">
+    <cfRule type="cellIs" dxfId="20" priority="27" operator="equal">
       <formula>"Nee"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V1:V42 V45:V193">
-    <cfRule type="beginsWith" dxfId="63" priority="118" operator="beginsWith" text="Gold">
+  <conditionalFormatting sqref="V1:V193">
+    <cfRule type="cellIs" dxfId="19" priority="28" operator="equal">
+      <formula>"Nee"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="18" priority="14" operator="beginsWith" text="Gold">
       <formula>LEFT(V1,LEN("Gold"))="Gold"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="128" operator="equal">
-      <formula>"Ja"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="129" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="25" operator="equal">
       <formula>"Gold"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="132" operator="equal">
-      <formula>"Nee"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E44 D43">
-    <cfRule type="containsText" dxfId="41" priority="1" operator="containsText" text="Ja">
-      <formula>NOT(ISERROR(SEARCH(("Ja"),(D43))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="2" operator="containsText" text="Nee">
-      <formula>NOT(ISERROR(SEARCH(("Nee"),(D43))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
-      <formula>"Via andere grondstof"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="equal">
-      <formula>"Oppervlakkig"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E43">
-    <cfRule type="containsText" dxfId="37" priority="7" operator="containsText" text="Ja">
-      <formula>NOT(ISERROR(SEARCH(("Ja"),(E43))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="8" operator="containsText" text="Nee">
-      <formula>NOT(ISERROR(SEARCH(("Nee"),(E43))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="9" operator="equal">
-      <formula>"Via andere grondstof"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="10" operator="equal">
-      <formula>"Oppervlakkig"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F43 H43:P44">
-    <cfRule type="cellIs" dxfId="33" priority="23" operator="equal">
-      <formula>"Via andere grondstof"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="26" operator="equal">
-      <formula>"Oppervlakkig"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z43:Z44 F43 H43:P44">
-    <cfRule type="containsText" dxfId="31" priority="16" operator="containsText" text="Nee">
-      <formula>NOT(ISERROR(SEARCH(("Nee"),(F43))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F43">
-    <cfRule type="containsText" dxfId="30" priority="13" operator="containsText" text="Ja">
-      <formula>NOT(ISERROR(SEARCH(("Ja"),(F43))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F43">
-    <cfRule type="cellIs" dxfId="29" priority="21" operator="equal">
-      <formula>"nvt"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F43">
-    <cfRule type="cellIs" dxfId="28" priority="12" operator="equal">
-      <formula>"Betrouwbaar"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z43:Z44 H43:P44">
-    <cfRule type="containsText" dxfId="27" priority="15" operator="containsText" text="Ja">
-      <formula>NOT(ISERROR(SEARCH(("Ja"),(H43))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H43:H44 R43:R44">
-    <cfRule type="cellIs" dxfId="26" priority="17" operator="equal">
-      <formula>"Betrouwbaar"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I43:P44">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I43:P44">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="num" val="1"/>
-        <cfvo type="num" val="3"/>
-        <cfvo type="num" val="5"/>
-        <color rgb="FF00B050"/>
-        <color rgb="FFFFEB84"/>
-        <color theme="5"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q43:Q44">
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="greaterThan">
-      <formula>2.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S43:T44">
-    <cfRule type="cellIs" dxfId="23" priority="19" operator="equal">
-      <formula>"mogelijk"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="24" operator="equal">
       <formula>"Ja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S43:S44">
-    <cfRule type="cellIs" dxfId="21" priority="18" operator="equal">
-      <formula>"Nee"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T43:T44">
-    <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
-      <formula>"nvt"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T43:T44">
-    <cfRule type="cellIs" dxfId="19" priority="27" operator="equal">
-      <formula>"Nee"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V43:V44">
-    <cfRule type="beginsWith" dxfId="18" priority="14" operator="beginsWith" text="Gold">
-      <formula>LEFT(V43,LEN("Gold"))="Gold"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="24" operator="equal">
-      <formula>"Ja"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="25" operator="equal">
-      <formula>"Gold"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="28" operator="equal">
-      <formula>"Nee"</formula>
+  <conditionalFormatting sqref="Z2:Z193 H43:P44 F42:F43">
+    <cfRule type="containsText" dxfId="15" priority="16" operator="containsText" text="Nee">
+      <formula>NOT(ISERROR(SEARCH(("Nee"),(F2))))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -17023,9 +16740,10 @@
     <hyperlink ref="G42" r:id="rId125" display="https://ec.europa.eu/eurostat/databrowser/view/cei_srm040__custom_20243394/default/table" xr:uid="{722B7B4D-A24C-4B12-9D56-A11515EBB8B3}"/>
     <hyperlink ref="G43" r:id="rId126" display="https://fred.stlouisfed.org/series/PCU4299304299301" xr:uid="{64D2A6E6-A8B8-428D-BA16-F72F190469C5}"/>
     <hyperlink ref="G44" r:id="rId127" display="https://fred.stlouisfed.org/series/PCU4299304299302" xr:uid="{DCABD4E3-FF52-4DF5-A57C-DC0392193462}"/>
+    <hyperlink ref="G4" r:id="rId128" xr:uid="{09A6BB08-7E50-4855-A12C-7F5FB260CB6C}"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <legacyDrawing r:id="rId128"/>
+  <legacyDrawing r:id="rId129"/>
 </worksheet>
 </file>
 
@@ -17149,16 +16867,16 @@
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
       <c r="I1" s="21"/>
-      <c r="J1" s="361" t="s">
+      <c r="J1" s="355" t="s">
         <v>337</v>
       </c>
-      <c r="K1" s="361"/>
-      <c r="L1" s="361"/>
-      <c r="M1" s="361"/>
-      <c r="N1" s="361"/>
-      <c r="O1" s="361"/>
-      <c r="P1" s="361"/>
-      <c r="Q1" s="361"/>
+      <c r="K1" s="355"/>
+      <c r="L1" s="355"/>
+      <c r="M1" s="355"/>
+      <c r="N1" s="355"/>
+      <c r="O1" s="355"/>
+      <c r="P1" s="355"/>
+      <c r="Q1" s="355"/>
       <c r="R1" s="21"/>
       <c r="S1" s="21"/>
       <c r="T1" s="20"/>
@@ -17285,7 +17003,7 @@
     </row>
     <row r="4" spans="1:25" ht="26.4">
       <c r="A4" s="20"/>
-      <c r="B4" s="313" t="s">
+      <c r="B4" s="327" t="s">
         <v>89</v>
       </c>
       <c r="C4" s="27" t="s">
@@ -17336,8 +17054,8 @@
     </row>
     <row r="5" spans="1:25" ht="13.2">
       <c r="A5" s="20"/>
-      <c r="B5" s="295"/>
-      <c r="C5" s="321" t="s">
+      <c r="B5" s="338"/>
+      <c r="C5" s="305" t="s">
         <v>97</v>
       </c>
       <c r="D5" s="26" t="s">
@@ -17383,8 +17101,8 @@
     </row>
     <row r="6" spans="1:25" ht="13.2">
       <c r="A6" s="20"/>
-      <c r="B6" s="295"/>
-      <c r="C6" s="295"/>
+      <c r="B6" s="338"/>
+      <c r="C6" s="338"/>
       <c r="D6" s="26" t="s">
         <v>100</v>
       </c>
@@ -17428,8 +17146,8 @@
     </row>
     <row r="7" spans="1:25" ht="13.2">
       <c r="A7" s="20"/>
-      <c r="B7" s="295"/>
-      <c r="C7" s="295"/>
+      <c r="B7" s="338"/>
+      <c r="C7" s="338"/>
       <c r="D7" s="25" t="s">
         <v>101</v>
       </c>
@@ -17473,8 +17191,8 @@
     </row>
     <row r="8" spans="1:25" ht="13.2">
       <c r="A8" s="20"/>
-      <c r="B8" s="295"/>
-      <c r="C8" s="296"/>
+      <c r="B8" s="338"/>
+      <c r="C8" s="336"/>
       <c r="D8" s="26" t="s">
         <v>102</v>
       </c>
@@ -17518,8 +17236,8 @@
     </row>
     <row r="9" spans="1:25" ht="26.4">
       <c r="A9" s="20"/>
-      <c r="B9" s="295"/>
-      <c r="C9" s="321" t="s">
+      <c r="B9" s="338"/>
+      <c r="C9" s="305" t="s">
         <v>103</v>
       </c>
       <c r="D9" s="29" t="s">
@@ -17565,8 +17283,8 @@
     </row>
     <row r="10" spans="1:25" ht="13.2">
       <c r="A10" s="20"/>
-      <c r="B10" s="295"/>
-      <c r="C10" s="295"/>
+      <c r="B10" s="338"/>
+      <c r="C10" s="338"/>
       <c r="D10" s="26" t="s">
         <v>106</v>
       </c>
@@ -17602,8 +17320,8 @@
     </row>
     <row r="11" spans="1:25" ht="13.2">
       <c r="A11" s="20"/>
-      <c r="B11" s="295"/>
-      <c r="C11" s="295"/>
+      <c r="B11" s="338"/>
+      <c r="C11" s="338"/>
       <c r="D11" s="26" t="s">
         <v>107</v>
       </c>
@@ -17643,8 +17361,8 @@
     </row>
     <row r="12" spans="1:25" ht="39.6">
       <c r="A12" s="20"/>
-      <c r="B12" s="295"/>
-      <c r="C12" s="295"/>
+      <c r="B12" s="338"/>
+      <c r="C12" s="338"/>
       <c r="D12" s="30" t="s">
         <v>109</v>
       </c>
@@ -17690,8 +17408,8 @@
     </row>
     <row r="13" spans="1:25" ht="13.2">
       <c r="A13" s="20"/>
-      <c r="B13" s="295"/>
-      <c r="C13" s="295"/>
+      <c r="B13" s="338"/>
+      <c r="C13" s="338"/>
       <c r="D13" s="30" t="s">
         <v>110</v>
       </c>
@@ -17735,8 +17453,8 @@
     </row>
     <row r="14" spans="1:25" ht="13.2">
       <c r="A14" s="20"/>
-      <c r="B14" s="295"/>
-      <c r="C14" s="296"/>
+      <c r="B14" s="338"/>
+      <c r="C14" s="336"/>
       <c r="D14" s="29" t="s">
         <v>111</v>
       </c>
@@ -17780,8 +17498,8 @@
     </row>
     <row r="15" spans="1:25" ht="42.6" customHeight="1">
       <c r="A15" s="20"/>
-      <c r="B15" s="295"/>
-      <c r="C15" s="321" t="s">
+      <c r="B15" s="338"/>
+      <c r="C15" s="305" t="s">
         <v>112</v>
       </c>
       <c r="D15" s="30" t="s">
@@ -17843,8 +17561,8 @@
     </row>
     <row r="16" spans="1:25" ht="52.8">
       <c r="A16" s="20"/>
-      <c r="B16" s="295"/>
-      <c r="C16" s="295"/>
+      <c r="B16" s="338"/>
+      <c r="C16" s="338"/>
       <c r="D16" s="30" t="s">
         <v>116</v>
       </c>
@@ -17892,8 +17610,8 @@
     </row>
     <row r="17" spans="1:25" ht="52.8">
       <c r="A17" s="20"/>
-      <c r="B17" s="295"/>
-      <c r="C17" s="296"/>
+      <c r="B17" s="338"/>
+      <c r="C17" s="336"/>
       <c r="D17" s="30" t="s">
         <v>120</v>
       </c>
@@ -17953,8 +17671,8 @@
     </row>
     <row r="18" spans="1:25" ht="26.4">
       <c r="A18" s="20"/>
-      <c r="B18" s="295"/>
-      <c r="C18" s="321" t="s">
+      <c r="B18" s="338"/>
+      <c r="C18" s="305" t="s">
         <v>122</v>
       </c>
       <c r="D18" s="27" t="s">
@@ -18004,8 +17722,8 @@
     </row>
     <row r="19" spans="1:25" ht="66">
       <c r="A19" s="20"/>
-      <c r="B19" s="295"/>
-      <c r="C19" s="295"/>
+      <c r="B19" s="338"/>
+      <c r="C19" s="338"/>
       <c r="D19" s="30" t="s">
         <v>123</v>
       </c>
@@ -18067,8 +17785,8 @@
     </row>
     <row r="20" spans="1:25" ht="37.5" customHeight="1">
       <c r="A20" s="20"/>
-      <c r="B20" s="295"/>
-      <c r="C20" s="296"/>
+      <c r="B20" s="338"/>
+      <c r="C20" s="336"/>
       <c r="D20" s="26" t="s">
         <v>126</v>
       </c>
@@ -18128,8 +17846,8 @@
     </row>
     <row r="21" spans="1:25" ht="26.4">
       <c r="A21" s="20"/>
-      <c r="B21" s="295"/>
-      <c r="C21" s="321" t="s">
+      <c r="B21" s="338"/>
+      <c r="C21" s="305" t="s">
         <v>128</v>
       </c>
       <c r="D21" s="32" t="s">
@@ -18179,8 +17897,8 @@
     </row>
     <row r="22" spans="1:25" ht="52.8">
       <c r="A22" s="20"/>
-      <c r="B22" s="295"/>
-      <c r="C22" s="295"/>
+      <c r="B22" s="338"/>
+      <c r="C22" s="338"/>
       <c r="D22" s="30" t="s">
         <v>129</v>
       </c>
@@ -18242,8 +17960,8 @@
     </row>
     <row r="23" spans="1:25" ht="52.8">
       <c r="A23" s="20"/>
-      <c r="B23" s="295"/>
-      <c r="C23" s="295"/>
+      <c r="B23" s="338"/>
+      <c r="C23" s="338"/>
       <c r="D23" s="30" t="s">
         <v>132</v>
       </c>
@@ -18305,8 +18023,8 @@
     </row>
     <row r="24" spans="1:25" ht="50.55" customHeight="1">
       <c r="A24" s="20"/>
-      <c r="B24" s="295"/>
-      <c r="C24" s="296"/>
+      <c r="B24" s="338"/>
+      <c r="C24" s="336"/>
       <c r="D24" s="30" t="s">
         <v>133</v>
       </c>
@@ -18370,8 +18088,8 @@
     </row>
     <row r="25" spans="1:25" ht="14.4">
       <c r="A25" s="20"/>
-      <c r="B25" s="295"/>
-      <c r="C25" s="294" t="s">
+      <c r="B25" s="338"/>
+      <c r="C25" s="319" t="s">
         <v>134</v>
       </c>
       <c r="D25" s="30" t="s">
@@ -18431,8 +18149,8 @@
     </row>
     <row r="26" spans="1:25" ht="39.6">
       <c r="A26" s="20"/>
-      <c r="B26" s="295"/>
-      <c r="C26" s="295"/>
+      <c r="B26" s="338"/>
+      <c r="C26" s="338"/>
       <c r="D26" s="26" t="s">
         <v>135</v>
       </c>
@@ -18487,7 +18205,7 @@
       <c r="U26" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="V26" s="320" t="s">
+      <c r="V26" s="326" t="s">
         <v>139</v>
       </c>
       <c r="W26" s="25"/>
@@ -18498,8 +18216,8 @@
     </row>
     <row r="27" spans="1:25" ht="39.6">
       <c r="A27" s="20"/>
-      <c r="B27" s="295"/>
-      <c r="C27" s="295"/>
+      <c r="B27" s="338"/>
+      <c r="C27" s="338"/>
       <c r="D27" s="26" t="s">
         <v>140</v>
       </c>
@@ -18554,7 +18272,7 @@
       <c r="U27" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="V27" s="295"/>
+      <c r="V27" s="338"/>
       <c r="W27" s="25"/>
       <c r="X27" s="25"/>
       <c r="Y27" s="25" t="s">
@@ -18563,8 +18281,8 @@
     </row>
     <row r="28" spans="1:25" ht="13.2">
       <c r="A28" s="20"/>
-      <c r="B28" s="295"/>
-      <c r="C28" s="295"/>
+      <c r="B28" s="338"/>
+      <c r="C28" s="338"/>
       <c r="D28" s="26" t="s">
         <v>142</v>
       </c>
@@ -18598,7 +18316,7 @@
       <c r="U28" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="V28" s="295"/>
+      <c r="V28" s="338"/>
       <c r="W28" s="25"/>
       <c r="X28" s="25"/>
       <c r="Y28" s="25" t="s">
@@ -18607,8 +18325,8 @@
     </row>
     <row r="29" spans="1:25" ht="89.55" customHeight="1">
       <c r="A29" s="20"/>
-      <c r="B29" s="295"/>
-      <c r="C29" s="295"/>
+      <c r="B29" s="338"/>
+      <c r="C29" s="338"/>
       <c r="D29" s="26" t="s">
         <v>143</v>
       </c>
@@ -18663,7 +18381,7 @@
       <c r="U29" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="V29" s="295"/>
+      <c r="V29" s="338"/>
       <c r="W29" s="25"/>
       <c r="X29" s="25"/>
       <c r="Y29" s="25" t="s">
@@ -18672,8 +18390,8 @@
     </row>
     <row r="30" spans="1:25" ht="39.6">
       <c r="A30" s="20"/>
-      <c r="B30" s="295"/>
-      <c r="C30" s="296"/>
+      <c r="B30" s="338"/>
+      <c r="C30" s="336"/>
       <c r="D30" s="26" t="s">
         <v>144</v>
       </c>
@@ -18728,7 +18446,7 @@
       <c r="U30" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="V30" s="296"/>
+      <c r="V30" s="336"/>
       <c r="W30" s="25"/>
       <c r="X30" s="25"/>
       <c r="Y30" s="25" t="s">
@@ -18737,7 +18455,7 @@
     </row>
     <row r="31" spans="1:25" ht="39.6">
       <c r="A31" s="20"/>
-      <c r="B31" s="295"/>
+      <c r="B31" s="338"/>
       <c r="C31" s="26" t="s">
         <v>145</v>
       </c>
@@ -18804,7 +18522,7 @@
     </row>
     <row r="32" spans="1:25" ht="92.4">
       <c r="A32" s="20"/>
-      <c r="B32" s="296"/>
+      <c r="B32" s="336"/>
       <c r="C32" s="33" t="s">
         <v>148</v>
       </c>
@@ -18855,7 +18573,7 @@
     </row>
     <row r="33" spans="1:25" ht="13.2">
       <c r="A33" s="20"/>
-      <c r="B33" s="351" t="s">
+      <c r="B33" s="363" t="s">
         <v>152</v>
       </c>
       <c r="C33" s="34" t="s">
@@ -18888,7 +18606,7 @@
       <c r="R33" s="26"/>
       <c r="S33" s="26"/>
       <c r="T33" s="25"/>
-      <c r="U33" s="358" t="s">
+      <c r="U33" s="360" t="s">
         <v>154</v>
       </c>
       <c r="V33" s="26"/>
@@ -18900,8 +18618,8 @@
     </row>
     <row r="34" spans="1:25" ht="13.2">
       <c r="A34" s="20"/>
-      <c r="B34" s="295"/>
-      <c r="C34" s="354" t="s">
+      <c r="B34" s="338"/>
+      <c r="C34" s="364" t="s">
         <v>97</v>
       </c>
       <c r="D34" s="29" t="s">
@@ -18931,7 +18649,7 @@
       <c r="R34" s="26"/>
       <c r="S34" s="26"/>
       <c r="T34" s="25"/>
-      <c r="U34" s="359"/>
+      <c r="U34" s="361"/>
       <c r="V34" s="26"/>
       <c r="W34" s="25"/>
       <c r="X34" s="25"/>
@@ -18941,8 +18659,8 @@
     </row>
     <row r="35" spans="1:25" ht="13.2">
       <c r="A35" s="20"/>
-      <c r="B35" s="295"/>
-      <c r="C35" s="295"/>
+      <c r="B35" s="338"/>
+      <c r="C35" s="338"/>
       <c r="D35" s="29" t="s">
         <v>100</v>
       </c>
@@ -18970,7 +18688,7 @@
       <c r="R35" s="26"/>
       <c r="S35" s="26"/>
       <c r="T35" s="25"/>
-      <c r="U35" s="359"/>
+      <c r="U35" s="361"/>
       <c r="V35" s="26"/>
       <c r="W35" s="25"/>
       <c r="X35" s="25"/>
@@ -18980,8 +18698,8 @@
     </row>
     <row r="36" spans="1:25" ht="52.8">
       <c r="A36" s="20"/>
-      <c r="B36" s="295"/>
-      <c r="C36" s="295"/>
+      <c r="B36" s="338"/>
+      <c r="C36" s="338"/>
       <c r="D36" s="36" t="s">
         <v>101</v>
       </c>
@@ -19009,7 +18727,7 @@
       <c r="R36" s="26"/>
       <c r="S36" s="26"/>
       <c r="T36" s="25"/>
-      <c r="U36" s="359"/>
+      <c r="U36" s="361"/>
       <c r="V36" s="26"/>
       <c r="W36" s="25"/>
       <c r="X36" s="25"/>
@@ -19019,8 +18737,8 @@
     </row>
     <row r="37" spans="1:25" ht="13.2">
       <c r="A37" s="20"/>
-      <c r="B37" s="295"/>
-      <c r="C37" s="296"/>
+      <c r="B37" s="338"/>
+      <c r="C37" s="336"/>
       <c r="D37" s="29" t="s">
         <v>102</v>
       </c>
@@ -19048,7 +18766,7 @@
       <c r="R37" s="26"/>
       <c r="S37" s="26"/>
       <c r="T37" s="25"/>
-      <c r="U37" s="359"/>
+      <c r="U37" s="361"/>
       <c r="V37" s="26"/>
       <c r="W37" s="25"/>
       <c r="X37" s="25"/>
@@ -19058,8 +18776,8 @@
     </row>
     <row r="38" spans="1:25" ht="26.4">
       <c r="A38" s="20"/>
-      <c r="B38" s="295"/>
-      <c r="C38" s="354" t="s">
+      <c r="B38" s="338"/>
+      <c r="C38" s="364" t="s">
         <v>156</v>
       </c>
       <c r="D38" s="29" t="s">
@@ -19089,7 +18807,7 @@
       <c r="R38" s="26"/>
       <c r="S38" s="26"/>
       <c r="T38" s="25"/>
-      <c r="U38" s="359"/>
+      <c r="U38" s="361"/>
       <c r="V38" s="26"/>
       <c r="W38" s="25"/>
       <c r="X38" s="25"/>
@@ -19099,8 +18817,8 @@
     </row>
     <row r="39" spans="1:25" ht="26.4">
       <c r="A39" s="20"/>
-      <c r="B39" s="295"/>
-      <c r="C39" s="295"/>
+      <c r="B39" s="338"/>
+      <c r="C39" s="338"/>
       <c r="D39" s="29" t="s">
         <v>109</v>
       </c>
@@ -19128,7 +18846,7 @@
       <c r="R39" s="26"/>
       <c r="S39" s="26"/>
       <c r="T39" s="25"/>
-      <c r="U39" s="359"/>
+      <c r="U39" s="361"/>
       <c r="V39" s="26"/>
       <c r="W39" s="25"/>
       <c r="X39" s="25"/>
@@ -19138,8 +18856,8 @@
     </row>
     <row r="40" spans="1:25" ht="13.2">
       <c r="A40" s="20"/>
-      <c r="B40" s="295"/>
-      <c r="C40" s="295"/>
+      <c r="B40" s="338"/>
+      <c r="C40" s="338"/>
       <c r="D40" s="29" t="s">
         <v>110</v>
       </c>
@@ -19167,7 +18885,7 @@
       <c r="R40" s="26"/>
       <c r="S40" s="26"/>
       <c r="T40" s="25"/>
-      <c r="U40" s="359"/>
+      <c r="U40" s="361"/>
       <c r="V40" s="26"/>
       <c r="W40" s="25"/>
       <c r="X40" s="25"/>
@@ -19177,8 +18895,8 @@
     </row>
     <row r="41" spans="1:25" ht="13.2">
       <c r="A41" s="20"/>
-      <c r="B41" s="295"/>
-      <c r="C41" s="295"/>
+      <c r="B41" s="338"/>
+      <c r="C41" s="338"/>
       <c r="D41" s="29" t="s">
         <v>106</v>
       </c>
@@ -19200,7 +18918,7 @@
       <c r="R41" s="26"/>
       <c r="S41" s="26"/>
       <c r="T41" s="25"/>
-      <c r="U41" s="359"/>
+      <c r="U41" s="361"/>
       <c r="V41" s="26"/>
       <c r="W41" s="25"/>
       <c r="X41" s="25"/>
@@ -19210,8 +18928,8 @@
     </row>
     <row r="42" spans="1:25" ht="13.2">
       <c r="A42" s="20"/>
-      <c r="B42" s="295"/>
-      <c r="C42" s="295"/>
+      <c r="B42" s="338"/>
+      <c r="C42" s="338"/>
       <c r="D42" s="29" t="s">
         <v>107</v>
       </c>
@@ -19233,7 +18951,7 @@
       <c r="R42" s="26"/>
       <c r="S42" s="26"/>
       <c r="T42" s="25"/>
-      <c r="U42" s="359"/>
+      <c r="U42" s="361"/>
       <c r="V42" s="26"/>
       <c r="W42" s="25"/>
       <c r="X42" s="25"/>
@@ -19243,8 +18961,8 @@
     </row>
     <row r="43" spans="1:25" ht="13.2">
       <c r="A43" s="20"/>
-      <c r="B43" s="295"/>
-      <c r="C43" s="296"/>
+      <c r="B43" s="338"/>
+      <c r="C43" s="336"/>
       <c r="D43" s="29" t="s">
         <v>111</v>
       </c>
@@ -19272,7 +18990,7 @@
       <c r="R43" s="26"/>
       <c r="S43" s="26"/>
       <c r="T43" s="25"/>
-      <c r="U43" s="359"/>
+      <c r="U43" s="361"/>
       <c r="V43" s="26"/>
       <c r="W43" s="25"/>
       <c r="X43" s="25"/>
@@ -19282,8 +19000,8 @@
     </row>
     <row r="44" spans="1:25" ht="13.2">
       <c r="A44" s="20"/>
-      <c r="B44" s="295"/>
-      <c r="C44" s="351" t="s">
+      <c r="B44" s="338"/>
+      <c r="C44" s="363" t="s">
         <v>112</v>
       </c>
       <c r="D44" s="29" t="s">
@@ -19307,7 +19025,7 @@
       <c r="R44" s="26"/>
       <c r="S44" s="26"/>
       <c r="T44" s="25"/>
-      <c r="U44" s="359"/>
+      <c r="U44" s="361"/>
       <c r="V44" s="26"/>
       <c r="W44" s="25"/>
       <c r="X44" s="25"/>
@@ -19317,8 +19035,8 @@
     </row>
     <row r="45" spans="1:25" ht="13.2">
       <c r="A45" s="20"/>
-      <c r="B45" s="295"/>
-      <c r="C45" s="295"/>
+      <c r="B45" s="338"/>
+      <c r="C45" s="338"/>
       <c r="D45" s="29" t="s">
         <v>116</v>
       </c>
@@ -19346,7 +19064,7 @@
       <c r="R45" s="26"/>
       <c r="S45" s="26"/>
       <c r="T45" s="25"/>
-      <c r="U45" s="359"/>
+      <c r="U45" s="361"/>
       <c r="V45" s="26"/>
       <c r="W45" s="25"/>
       <c r="X45" s="25"/>
@@ -19356,8 +19074,8 @@
     </row>
     <row r="46" spans="1:25" ht="13.2">
       <c r="A46" s="20"/>
-      <c r="B46" s="295"/>
-      <c r="C46" s="296"/>
+      <c r="B46" s="338"/>
+      <c r="C46" s="336"/>
       <c r="D46" s="29" t="s">
         <v>120</v>
       </c>
@@ -19385,7 +19103,7 @@
       <c r="R46" s="26"/>
       <c r="S46" s="26"/>
       <c r="T46" s="25"/>
-      <c r="U46" s="359"/>
+      <c r="U46" s="361"/>
       <c r="V46" s="26"/>
       <c r="W46" s="25"/>
       <c r="X46" s="25"/>
@@ -19395,8 +19113,8 @@
     </row>
     <row r="47" spans="1:25" ht="13.2">
       <c r="A47" s="20"/>
-      <c r="B47" s="295"/>
-      <c r="C47" s="354" t="s">
+      <c r="B47" s="338"/>
+      <c r="C47" s="364" t="s">
         <v>122</v>
       </c>
       <c r="D47" s="34" t="s">
@@ -19426,7 +19144,7 @@
       <c r="R47" s="26"/>
       <c r="S47" s="26"/>
       <c r="T47" s="25"/>
-      <c r="U47" s="359"/>
+      <c r="U47" s="361"/>
       <c r="V47" s="26"/>
       <c r="W47" s="25"/>
       <c r="X47" s="25"/>
@@ -19436,8 +19154,8 @@
     </row>
     <row r="48" spans="1:25" ht="13.2">
       <c r="A48" s="20"/>
-      <c r="B48" s="295"/>
-      <c r="C48" s="295"/>
+      <c r="B48" s="338"/>
+      <c r="C48" s="338"/>
       <c r="D48" s="29" t="s">
         <v>123</v>
       </c>
@@ -19465,7 +19183,7 @@
       <c r="R48" s="26"/>
       <c r="S48" s="26"/>
       <c r="T48" s="25"/>
-      <c r="U48" s="359"/>
+      <c r="U48" s="361"/>
       <c r="V48" s="26"/>
       <c r="W48" s="25"/>
       <c r="X48" s="25"/>
@@ -19475,8 +19193,8 @@
     </row>
     <row r="49" spans="1:25" ht="13.2">
       <c r="A49" s="20"/>
-      <c r="B49" s="295"/>
-      <c r="C49" s="296"/>
+      <c r="B49" s="338"/>
+      <c r="C49" s="336"/>
       <c r="D49" s="29" t="s">
         <v>126</v>
       </c>
@@ -19504,7 +19222,7 @@
       <c r="R49" s="26"/>
       <c r="S49" s="26"/>
       <c r="T49" s="25"/>
-      <c r="U49" s="359"/>
+      <c r="U49" s="361"/>
       <c r="V49" s="26"/>
       <c r="W49" s="25"/>
       <c r="X49" s="25"/>
@@ -19514,8 +19232,8 @@
     </row>
     <row r="50" spans="1:25" ht="13.2">
       <c r="A50" s="20"/>
-      <c r="B50" s="295"/>
-      <c r="C50" s="354" t="s">
+      <c r="B50" s="338"/>
+      <c r="C50" s="364" t="s">
         <v>128</v>
       </c>
       <c r="D50" s="38" t="s">
@@ -19545,7 +19263,7 @@
       <c r="R50" s="26"/>
       <c r="S50" s="26"/>
       <c r="T50" s="25"/>
-      <c r="U50" s="359"/>
+      <c r="U50" s="361"/>
       <c r="V50" s="26"/>
       <c r="W50" s="25"/>
       <c r="X50" s="25"/>
@@ -19555,8 +19273,8 @@
     </row>
     <row r="51" spans="1:25" ht="13.2">
       <c r="A51" s="20"/>
-      <c r="B51" s="295"/>
-      <c r="C51" s="295"/>
+      <c r="B51" s="338"/>
+      <c r="C51" s="338"/>
       <c r="D51" s="29" t="s">
         <v>129</v>
       </c>
@@ -19584,7 +19302,7 @@
       <c r="R51" s="26"/>
       <c r="S51" s="26"/>
       <c r="T51" s="25"/>
-      <c r="U51" s="359"/>
+      <c r="U51" s="361"/>
       <c r="V51" s="26"/>
       <c r="W51" s="25"/>
       <c r="X51" s="25"/>
@@ -19594,8 +19312,8 @@
     </row>
     <row r="52" spans="1:25" ht="13.2">
       <c r="A52" s="20"/>
-      <c r="B52" s="295"/>
-      <c r="C52" s="295"/>
+      <c r="B52" s="338"/>
+      <c r="C52" s="338"/>
       <c r="D52" s="29" t="s">
         <v>132</v>
       </c>
@@ -19623,7 +19341,7 @@
       <c r="R52" s="26"/>
       <c r="S52" s="26"/>
       <c r="T52" s="25"/>
-      <c r="U52" s="359"/>
+      <c r="U52" s="361"/>
       <c r="V52" s="26"/>
       <c r="W52" s="25"/>
       <c r="X52" s="25"/>
@@ -19633,8 +19351,8 @@
     </row>
     <row r="53" spans="1:25" ht="13.2">
       <c r="A53" s="20"/>
-      <c r="B53" s="295"/>
-      <c r="C53" s="296"/>
+      <c r="B53" s="338"/>
+      <c r="C53" s="336"/>
       <c r="D53" s="29" t="s">
         <v>133</v>
       </c>
@@ -19662,7 +19380,7 @@
       <c r="R53" s="26"/>
       <c r="S53" s="26"/>
       <c r="T53" s="25"/>
-      <c r="U53" s="359"/>
+      <c r="U53" s="361"/>
       <c r="V53" s="26"/>
       <c r="W53" s="25"/>
       <c r="X53" s="25"/>
@@ -19672,8 +19390,8 @@
     </row>
     <row r="54" spans="1:25" ht="13.2">
       <c r="A54" s="20"/>
-      <c r="B54" s="295"/>
-      <c r="C54" s="351" t="s">
+      <c r="B54" s="338"/>
+      <c r="C54" s="363" t="s">
         <v>134</v>
       </c>
       <c r="D54" s="29" t="s">
@@ -19703,7 +19421,7 @@
       <c r="R54" s="26"/>
       <c r="S54" s="26"/>
       <c r="T54" s="25"/>
-      <c r="U54" s="359"/>
+      <c r="U54" s="361"/>
       <c r="V54" s="26"/>
       <c r="W54" s="25"/>
       <c r="X54" s="25"/>
@@ -19713,8 +19431,8 @@
     </row>
     <row r="55" spans="1:25" ht="13.2">
       <c r="A55" s="20"/>
-      <c r="B55" s="295"/>
-      <c r="C55" s="295"/>
+      <c r="B55" s="338"/>
+      <c r="C55" s="338"/>
       <c r="D55" s="29" t="s">
         <v>140</v>
       </c>
@@ -19742,7 +19460,7 @@
       <c r="R55" s="26"/>
       <c r="S55" s="26"/>
       <c r="T55" s="25"/>
-      <c r="U55" s="359"/>
+      <c r="U55" s="361"/>
       <c r="V55" s="26"/>
       <c r="W55" s="25"/>
       <c r="X55" s="25"/>
@@ -19752,8 +19470,8 @@
     </row>
     <row r="56" spans="1:25" ht="13.2">
       <c r="A56" s="20"/>
-      <c r="B56" s="295"/>
-      <c r="C56" s="295"/>
+      <c r="B56" s="338"/>
+      <c r="C56" s="338"/>
       <c r="D56" s="29" t="s">
         <v>142</v>
       </c>
@@ -19781,7 +19499,7 @@
       <c r="R56" s="26"/>
       <c r="S56" s="26"/>
       <c r="T56" s="25"/>
-      <c r="U56" s="359"/>
+      <c r="U56" s="361"/>
       <c r="V56" s="26"/>
       <c r="W56" s="25"/>
       <c r="X56" s="25"/>
@@ -19791,8 +19509,8 @@
     </row>
     <row r="57" spans="1:25" ht="13.2">
       <c r="A57" s="20"/>
-      <c r="B57" s="295"/>
-      <c r="C57" s="295"/>
+      <c r="B57" s="338"/>
+      <c r="C57" s="338"/>
       <c r="D57" s="29" t="s">
         <v>143</v>
       </c>
@@ -19820,7 +19538,7 @@
       <c r="R57" s="26"/>
       <c r="S57" s="26"/>
       <c r="T57" s="25"/>
-      <c r="U57" s="359"/>
+      <c r="U57" s="361"/>
       <c r="V57" s="26"/>
       <c r="W57" s="25"/>
       <c r="X57" s="25"/>
@@ -19830,8 +19548,8 @@
     </row>
     <row r="58" spans="1:25" ht="13.2">
       <c r="A58" s="20"/>
-      <c r="B58" s="296"/>
-      <c r="C58" s="296"/>
+      <c r="B58" s="336"/>
+      <c r="C58" s="336"/>
       <c r="D58" s="29" t="s">
         <v>144</v>
       </c>
@@ -19859,7 +19577,7 @@
       <c r="R58" s="26"/>
       <c r="S58" s="26"/>
       <c r="T58" s="25"/>
-      <c r="U58" s="360"/>
+      <c r="U58" s="362"/>
       <c r="V58" s="26"/>
       <c r="W58" s="25"/>
       <c r="X58" s="25"/>
@@ -19869,7 +19587,7 @@
     </row>
     <row r="59" spans="1:25" ht="13.2">
       <c r="A59" s="20"/>
-      <c r="B59" s="294" t="s">
+      <c r="B59" s="319" t="s">
         <v>157</v>
       </c>
       <c r="C59" s="27" t="s">
@@ -19914,8 +19632,8 @@
     </row>
     <row r="60" spans="1:25" ht="13.2">
       <c r="A60" s="20"/>
-      <c r="B60" s="295"/>
-      <c r="C60" s="321" t="s">
+      <c r="B60" s="338"/>
+      <c r="C60" s="305" t="s">
         <v>97</v>
       </c>
       <c r="D60" s="26" t="s">
@@ -19957,8 +19675,8 @@
     </row>
     <row r="61" spans="1:25" ht="13.2">
       <c r="A61" s="20"/>
-      <c r="B61" s="295"/>
-      <c r="C61" s="295"/>
+      <c r="B61" s="338"/>
+      <c r="C61" s="338"/>
       <c r="D61" s="26" t="s">
         <v>100</v>
       </c>
@@ -19998,8 +19716,8 @@
     </row>
     <row r="62" spans="1:25" ht="13.2">
       <c r="A62" s="20"/>
-      <c r="B62" s="295"/>
-      <c r="C62" s="295"/>
+      <c r="B62" s="338"/>
+      <c r="C62" s="338"/>
       <c r="D62" s="25" t="s">
         <v>101</v>
       </c>
@@ -20039,8 +19757,8 @@
     </row>
     <row r="63" spans="1:25" ht="13.2">
       <c r="A63" s="20"/>
-      <c r="B63" s="295"/>
-      <c r="C63" s="296"/>
+      <c r="B63" s="338"/>
+      <c r="C63" s="336"/>
       <c r="D63" s="26" t="s">
         <v>102</v>
       </c>
@@ -20080,8 +19798,8 @@
     </row>
     <row r="64" spans="1:25" ht="26.4">
       <c r="A64" s="20"/>
-      <c r="B64" s="295"/>
-      <c r="C64" s="321" t="s">
+      <c r="B64" s="338"/>
+      <c r="C64" s="305" t="s">
         <v>103</v>
       </c>
       <c r="D64" s="26" t="s">
@@ -20123,8 +19841,8 @@
     </row>
     <row r="65" spans="1:25" ht="26.4">
       <c r="A65" s="20"/>
-      <c r="B65" s="295"/>
-      <c r="C65" s="295"/>
+      <c r="B65" s="338"/>
+      <c r="C65" s="338"/>
       <c r="D65" s="26" t="s">
         <v>109</v>
       </c>
@@ -20164,8 +19882,8 @@
     </row>
     <row r="66" spans="1:25" ht="13.2">
       <c r="A66" s="20"/>
-      <c r="B66" s="295"/>
-      <c r="C66" s="295"/>
+      <c r="B66" s="338"/>
+      <c r="C66" s="338"/>
       <c r="D66" s="26" t="s">
         <v>110</v>
       </c>
@@ -20205,8 +19923,8 @@
     </row>
     <row r="67" spans="1:25" ht="13.2">
       <c r="A67" s="20"/>
-      <c r="B67" s="295"/>
-      <c r="C67" s="296"/>
+      <c r="B67" s="338"/>
+      <c r="C67" s="336"/>
       <c r="D67" s="26" t="s">
         <v>111</v>
       </c>
@@ -20246,8 +19964,8 @@
     </row>
     <row r="68" spans="1:25" ht="52.8">
       <c r="A68" s="20"/>
-      <c r="B68" s="295"/>
-      <c r="C68" s="294" t="s">
+      <c r="B68" s="338"/>
+      <c r="C68" s="319" t="s">
         <v>112</v>
       </c>
       <c r="D68" s="26" t="s">
@@ -20299,8 +20017,8 @@
     </row>
     <row r="69" spans="1:25" ht="52.8">
       <c r="A69" s="20"/>
-      <c r="B69" s="295"/>
-      <c r="C69" s="295"/>
+      <c r="B69" s="338"/>
+      <c r="C69" s="338"/>
       <c r="D69" s="26" t="s">
         <v>116</v>
       </c>
@@ -20355,8 +20073,8 @@
     </row>
     <row r="70" spans="1:25" ht="39.6">
       <c r="A70" s="20"/>
-      <c r="B70" s="295"/>
-      <c r="C70" s="296"/>
+      <c r="B70" s="338"/>
+      <c r="C70" s="336"/>
       <c r="D70" s="26" t="s">
         <v>120</v>
       </c>
@@ -20411,8 +20129,8 @@
     </row>
     <row r="71" spans="1:25" ht="13.2">
       <c r="A71" s="20"/>
-      <c r="B71" s="295"/>
-      <c r="C71" s="321" t="s">
+      <c r="B71" s="338"/>
+      <c r="C71" s="305" t="s">
         <v>122</v>
       </c>
       <c r="D71" s="27" t="s">
@@ -20457,8 +20175,8 @@
     </row>
     <row r="72" spans="1:25" ht="105.6">
       <c r="A72" s="20"/>
-      <c r="B72" s="295"/>
-      <c r="C72" s="295"/>
+      <c r="B72" s="338"/>
+      <c r="C72" s="338"/>
       <c r="D72" s="26" t="s">
         <v>123</v>
       </c>
@@ -20511,8 +20229,8 @@
     </row>
     <row r="73" spans="1:25" ht="13.2">
       <c r="A73" s="20"/>
-      <c r="B73" s="295"/>
-      <c r="C73" s="296"/>
+      <c r="B73" s="338"/>
+      <c r="C73" s="336"/>
       <c r="D73" s="26" t="s">
         <v>126</v>
       </c>
@@ -20567,8 +20285,8 @@
     </row>
     <row r="74" spans="1:25" ht="39.6">
       <c r="A74" s="20"/>
-      <c r="B74" s="295"/>
-      <c r="C74" s="321" t="s">
+      <c r="B74" s="338"/>
+      <c r="C74" s="305" t="s">
         <v>128</v>
       </c>
       <c r="D74" s="39" t="s">
@@ -20625,8 +20343,8 @@
     </row>
     <row r="75" spans="1:25" ht="66">
       <c r="A75" s="20"/>
-      <c r="B75" s="295"/>
-      <c r="C75" s="295"/>
+      <c r="B75" s="338"/>
+      <c r="C75" s="338"/>
       <c r="D75" s="26" t="s">
         <v>129</v>
       </c>
@@ -20682,8 +20400,8 @@
     </row>
     <row r="76" spans="1:25" ht="39.6">
       <c r="A76" s="20"/>
-      <c r="B76" s="295"/>
-      <c r="C76" s="295"/>
+      <c r="B76" s="338"/>
+      <c r="C76" s="338"/>
       <c r="D76" s="26" t="s">
         <v>132</v>
       </c>
@@ -20725,8 +20443,8 @@
     </row>
     <row r="77" spans="1:25" ht="13.2">
       <c r="A77" s="20"/>
-      <c r="B77" s="295"/>
-      <c r="C77" s="296"/>
+      <c r="B77" s="338"/>
+      <c r="C77" s="336"/>
       <c r="D77" s="26" t="s">
         <v>133</v>
       </c>
@@ -20767,8 +20485,8 @@
     </row>
     <row r="78" spans="1:25" ht="26.4">
       <c r="A78" s="20"/>
-      <c r="B78" s="295"/>
-      <c r="C78" s="294" t="s">
+      <c r="B78" s="338"/>
+      <c r="C78" s="319" t="s">
         <v>134</v>
       </c>
       <c r="D78" s="26" t="s">
@@ -20808,8 +20526,8 @@
     </row>
     <row r="79" spans="1:25" ht="13.2">
       <c r="A79" s="20"/>
-      <c r="B79" s="295"/>
-      <c r="C79" s="295"/>
+      <c r="B79" s="338"/>
+      <c r="C79" s="338"/>
       <c r="D79" s="26" t="s">
         <v>135</v>
       </c>
@@ -20848,8 +20566,8 @@
     </row>
     <row r="80" spans="1:25" ht="13.2">
       <c r="A80" s="20"/>
-      <c r="B80" s="295"/>
-      <c r="C80" s="295"/>
+      <c r="B80" s="338"/>
+      <c r="C80" s="338"/>
       <c r="D80" s="26" t="s">
         <v>140</v>
       </c>
@@ -20888,8 +20606,8 @@
     </row>
     <row r="81" spans="1:25" ht="13.2">
       <c r="A81" s="20"/>
-      <c r="B81" s="295"/>
-      <c r="C81" s="295"/>
+      <c r="B81" s="338"/>
+      <c r="C81" s="338"/>
       <c r="D81" s="26" t="s">
         <v>142</v>
       </c>
@@ -20926,8 +20644,8 @@
     </row>
     <row r="82" spans="1:25" ht="26.4">
       <c r="A82" s="20"/>
-      <c r="B82" s="295"/>
-      <c r="C82" s="295"/>
+      <c r="B82" s="338"/>
+      <c r="C82" s="338"/>
       <c r="D82" s="26" t="s">
         <v>143</v>
       </c>
@@ -20966,8 +20684,8 @@
     </row>
     <row r="83" spans="1:25" ht="13.2">
       <c r="A83" s="20"/>
-      <c r="B83" s="296"/>
-      <c r="C83" s="296"/>
+      <c r="B83" s="336"/>
+      <c r="C83" s="336"/>
       <c r="D83" s="26" t="s">
         <v>144</v>
       </c>
@@ -21006,7 +20724,7 @@
     </row>
     <row r="84" spans="1:25" ht="26.4">
       <c r="A84" s="20"/>
-      <c r="B84" s="352" t="s">
+      <c r="B84" s="368" t="s">
         <v>170</v>
       </c>
       <c r="C84" s="26" t="s">
@@ -21049,8 +20767,8 @@
     </row>
     <row r="85" spans="1:25" ht="13.2">
       <c r="A85" s="20"/>
-      <c r="B85" s="295"/>
-      <c r="C85" s="294" t="s">
+      <c r="B85" s="338"/>
+      <c r="C85" s="319" t="s">
         <v>97</v>
       </c>
       <c r="D85" s="26" t="s">
@@ -21089,8 +20807,8 @@
     </row>
     <row r="86" spans="1:25" ht="13.2">
       <c r="A86" s="20"/>
-      <c r="B86" s="295"/>
-      <c r="C86" s="295"/>
+      <c r="B86" s="338"/>
+      <c r="C86" s="338"/>
       <c r="D86" s="26" t="s">
         <v>100</v>
       </c>
@@ -21127,8 +20845,8 @@
     </row>
     <row r="87" spans="1:25" ht="13.2">
       <c r="A87" s="20"/>
-      <c r="B87" s="295"/>
-      <c r="C87" s="295"/>
+      <c r="B87" s="338"/>
+      <c r="C87" s="338"/>
       <c r="D87" s="25" t="s">
         <v>101</v>
       </c>
@@ -21165,8 +20883,8 @@
     </row>
     <row r="88" spans="1:25" ht="13.2">
       <c r="A88" s="20"/>
-      <c r="B88" s="295"/>
-      <c r="C88" s="296"/>
+      <c r="B88" s="338"/>
+      <c r="C88" s="336"/>
       <c r="D88" s="26" t="s">
         <v>102</v>
       </c>
@@ -21203,8 +20921,8 @@
     </row>
     <row r="89" spans="1:25" ht="39.6">
       <c r="A89" s="20"/>
-      <c r="B89" s="295"/>
-      <c r="C89" s="294" t="s">
+      <c r="B89" s="338"/>
+      <c r="C89" s="319" t="s">
         <v>103</v>
       </c>
       <c r="D89" s="26" t="s">
@@ -21245,8 +20963,8 @@
     </row>
     <row r="90" spans="1:25" ht="26.4">
       <c r="A90" s="20"/>
-      <c r="B90" s="295"/>
-      <c r="C90" s="295"/>
+      <c r="B90" s="338"/>
+      <c r="C90" s="338"/>
       <c r="D90" s="26" t="s">
         <v>109</v>
       </c>
@@ -21286,8 +21004,8 @@
     </row>
     <row r="91" spans="1:25" ht="26.4">
       <c r="A91" s="20"/>
-      <c r="B91" s="295"/>
-      <c r="C91" s="295"/>
+      <c r="B91" s="338"/>
+      <c r="C91" s="338"/>
       <c r="D91" s="26" t="s">
         <v>110</v>
       </c>
@@ -21327,8 +21045,8 @@
     </row>
     <row r="92" spans="1:25" ht="13.2">
       <c r="A92" s="20"/>
-      <c r="B92" s="295"/>
-      <c r="C92" s="296"/>
+      <c r="B92" s="338"/>
+      <c r="C92" s="336"/>
       <c r="D92" s="26" t="s">
         <v>111</v>
       </c>
@@ -21366,8 +21084,8 @@
     </row>
     <row r="93" spans="1:25" ht="13.2">
       <c r="A93" s="20"/>
-      <c r="B93" s="295"/>
-      <c r="C93" s="294" t="s">
+      <c r="B93" s="338"/>
+      <c r="C93" s="319" t="s">
         <v>112</v>
       </c>
       <c r="D93" s="26" t="s">
@@ -21401,8 +21119,8 @@
     </row>
     <row r="94" spans="1:25" ht="13.2">
       <c r="A94" s="20"/>
-      <c r="B94" s="295"/>
-      <c r="C94" s="295"/>
+      <c r="B94" s="338"/>
+      <c r="C94" s="338"/>
       <c r="D94" s="26" t="s">
         <v>116</v>
       </c>
@@ -21440,8 +21158,8 @@
     </row>
     <row r="95" spans="1:25" ht="13.2">
       <c r="A95" s="20"/>
-      <c r="B95" s="295"/>
-      <c r="C95" s="296"/>
+      <c r="B95" s="338"/>
+      <c r="C95" s="336"/>
       <c r="D95" s="26" t="s">
         <v>120</v>
       </c>
@@ -21479,8 +21197,8 @@
     </row>
     <row r="96" spans="1:25" ht="13.2">
       <c r="A96" s="20"/>
-      <c r="B96" s="295"/>
-      <c r="C96" s="294" t="s">
+      <c r="B96" s="338"/>
+      <c r="C96" s="319" t="s">
         <v>122</v>
       </c>
       <c r="D96" s="26" t="s">
@@ -21520,8 +21238,8 @@
     </row>
     <row r="97" spans="1:25" ht="13.2">
       <c r="A97" s="20"/>
-      <c r="B97" s="295"/>
-      <c r="C97" s="295"/>
+      <c r="B97" s="338"/>
+      <c r="C97" s="338"/>
       <c r="D97" s="26" t="s">
         <v>123</v>
       </c>
@@ -21559,8 +21277,8 @@
     </row>
     <row r="98" spans="1:25" ht="13.2">
       <c r="A98" s="20"/>
-      <c r="B98" s="295"/>
-      <c r="C98" s="296"/>
+      <c r="B98" s="338"/>
+      <c r="C98" s="336"/>
       <c r="D98" s="26" t="s">
         <v>126</v>
       </c>
@@ -21598,8 +21316,8 @@
     </row>
     <row r="99" spans="1:25" ht="13.2">
       <c r="A99" s="20"/>
-      <c r="B99" s="295"/>
-      <c r="C99" s="294" t="s">
+      <c r="B99" s="338"/>
+      <c r="C99" s="319" t="s">
         <v>128</v>
       </c>
       <c r="D99" s="20" t="s">
@@ -21639,8 +21357,8 @@
     </row>
     <row r="100" spans="1:25" ht="13.2">
       <c r="A100" s="20"/>
-      <c r="B100" s="295"/>
-      <c r="C100" s="295"/>
+      <c r="B100" s="338"/>
+      <c r="C100" s="338"/>
       <c r="D100" s="26" t="s">
         <v>129</v>
       </c>
@@ -21678,8 +21396,8 @@
     </row>
     <row r="101" spans="1:25" ht="13.2">
       <c r="A101" s="20"/>
-      <c r="B101" s="295"/>
-      <c r="C101" s="295"/>
+      <c r="B101" s="338"/>
+      <c r="C101" s="338"/>
       <c r="D101" s="26" t="s">
         <v>132</v>
       </c>
@@ -21717,8 +21435,8 @@
     </row>
     <row r="102" spans="1:25" ht="13.2">
       <c r="A102" s="20"/>
-      <c r="B102" s="295"/>
-      <c r="C102" s="296"/>
+      <c r="B102" s="338"/>
+      <c r="C102" s="336"/>
       <c r="D102" s="26" t="s">
         <v>133</v>
       </c>
@@ -21756,8 +21474,8 @@
     </row>
     <row r="103" spans="1:25" ht="13.2">
       <c r="A103" s="20"/>
-      <c r="B103" s="295"/>
-      <c r="C103" s="294" t="s">
+      <c r="B103" s="338"/>
+      <c r="C103" s="319" t="s">
         <v>134</v>
       </c>
       <c r="D103" s="26" t="s">
@@ -21797,8 +21515,8 @@
     </row>
     <row r="104" spans="1:25" ht="13.2">
       <c r="A104" s="20"/>
-      <c r="B104" s="295"/>
-      <c r="C104" s="295"/>
+      <c r="B104" s="338"/>
+      <c r="C104" s="338"/>
       <c r="D104" s="26" t="s">
         <v>140</v>
       </c>
@@ -21836,8 +21554,8 @@
     </row>
     <row r="105" spans="1:25" ht="13.2">
       <c r="A105" s="20"/>
-      <c r="B105" s="295"/>
-      <c r="C105" s="295"/>
+      <c r="B105" s="338"/>
+      <c r="C105" s="338"/>
       <c r="D105" s="26" t="s">
         <v>142</v>
       </c>
@@ -21875,8 +21593,8 @@
     </row>
     <row r="106" spans="1:25" ht="13.2">
       <c r="A106" s="20"/>
-      <c r="B106" s="295"/>
-      <c r="C106" s="295"/>
+      <c r="B106" s="338"/>
+      <c r="C106" s="338"/>
       <c r="D106" s="26" t="s">
         <v>143</v>
       </c>
@@ -21914,8 +21632,8 @@
     </row>
     <row r="107" spans="1:25" ht="13.2">
       <c r="A107" s="20"/>
-      <c r="B107" s="296"/>
-      <c r="C107" s="296"/>
+      <c r="B107" s="336"/>
+      <c r="C107" s="336"/>
       <c r="D107" s="26" t="s">
         <v>144</v>
       </c>
@@ -21953,10 +21671,10 @@
     </row>
     <row r="108" spans="1:25" ht="13.2">
       <c r="A108" s="20"/>
-      <c r="B108" s="313" t="s">
+      <c r="B108" s="327" t="s">
         <v>12</v>
       </c>
-      <c r="C108" s="321" t="s">
+      <c r="C108" s="305" t="s">
         <v>175</v>
       </c>
       <c r="D108" s="30" t="s">
@@ -22008,8 +21726,8 @@
     </row>
     <row r="109" spans="1:25" ht="13.2">
       <c r="A109" s="20"/>
-      <c r="B109" s="295"/>
-      <c r="C109" s="296"/>
+      <c r="B109" s="338"/>
+      <c r="C109" s="336"/>
       <c r="D109" s="41" t="s">
         <v>183</v>
       </c>
@@ -22061,8 +21779,8 @@
     </row>
     <row r="110" spans="1:25" ht="13.2">
       <c r="A110" s="20"/>
-      <c r="B110" s="295"/>
-      <c r="C110" s="321" t="s">
+      <c r="B110" s="338"/>
+      <c r="C110" s="305" t="s">
         <v>188</v>
       </c>
       <c r="D110" s="30" t="s">
@@ -22114,8 +21832,8 @@
     </row>
     <row r="111" spans="1:25" ht="13.2">
       <c r="A111" s="20"/>
-      <c r="B111" s="295"/>
-      <c r="C111" s="355"/>
+      <c r="B111" s="338"/>
+      <c r="C111" s="356"/>
       <c r="D111" s="46" t="s">
         <v>370</v>
       </c>
@@ -22157,8 +21875,8 @@
     </row>
     <row r="112" spans="1:25" ht="26.4">
       <c r="A112" s="20"/>
-      <c r="B112" s="295"/>
-      <c r="C112" s="296"/>
+      <c r="B112" s="338"/>
+      <c r="C112" s="336"/>
       <c r="D112" s="41" t="s">
         <v>373</v>
       </c>
@@ -22210,8 +21928,8 @@
     </row>
     <row r="113" spans="1:25" ht="13.2">
       <c r="A113" s="20"/>
-      <c r="B113" s="295"/>
-      <c r="C113" s="362" t="s">
+      <c r="B113" s="338"/>
+      <c r="C113" s="357" t="s">
         <v>200</v>
       </c>
       <c r="D113" s="41" t="s">
@@ -22241,8 +21959,8 @@
     </row>
     <row r="114" spans="1:25" ht="13.2">
       <c r="A114" s="20"/>
-      <c r="B114" s="295"/>
-      <c r="C114" s="363"/>
+      <c r="B114" s="338"/>
+      <c r="C114" s="358"/>
       <c r="D114" s="41" t="s">
         <v>377</v>
       </c>
@@ -22270,8 +21988,8 @@
     </row>
     <row r="115" spans="1:25" ht="13.2">
       <c r="A115" s="20"/>
-      <c r="B115" s="295"/>
-      <c r="C115" s="364"/>
+      <c r="B115" s="338"/>
+      <c r="C115" s="359"/>
       <c r="D115" s="41" t="s">
         <v>378</v>
       </c>
@@ -22299,7 +22017,7 @@
     </row>
     <row r="116" spans="1:25" ht="13.2">
       <c r="A116" s="20"/>
-      <c r="B116" s="296"/>
+      <c r="B116" s="336"/>
       <c r="C116" s="27" t="s">
         <v>379</v>
       </c>
@@ -22355,10 +22073,10 @@
     </row>
     <row r="117" spans="1:25" ht="13.2">
       <c r="A117" s="20"/>
-      <c r="B117" s="313" t="s">
+      <c r="B117" s="327" t="s">
         <v>11</v>
       </c>
-      <c r="C117" s="321" t="s">
+      <c r="C117" s="305" t="s">
         <v>201</v>
       </c>
       <c r="D117" s="44" t="s">
@@ -22408,8 +22126,8 @@
     </row>
     <row r="118" spans="1:25" ht="13.2">
       <c r="A118" s="20"/>
-      <c r="B118" s="314"/>
-      <c r="C118" s="355"/>
+      <c r="B118" s="334"/>
+      <c r="C118" s="356"/>
       <c r="D118" s="44" t="s">
         <v>206</v>
       </c>
@@ -22453,8 +22171,8 @@
     </row>
     <row r="119" spans="1:25" ht="13.2">
       <c r="A119" s="20"/>
-      <c r="B119" s="295"/>
-      <c r="C119" s="296"/>
+      <c r="B119" s="338"/>
+      <c r="C119" s="336"/>
       <c r="D119" s="30" t="s">
         <v>211</v>
       </c>
@@ -22500,8 +22218,8 @@
     </row>
     <row r="120" spans="1:25" ht="13.2">
       <c r="A120" s="20"/>
-      <c r="B120" s="295"/>
-      <c r="C120" s="321" t="s">
+      <c r="B120" s="338"/>
+      <c r="C120" s="305" t="s">
         <v>216</v>
       </c>
       <c r="D120" s="26" t="s">
@@ -22545,8 +22263,8 @@
     </row>
     <row r="121" spans="1:25" ht="13.2">
       <c r="A121" s="20"/>
-      <c r="B121" s="295"/>
-      <c r="C121" s="295"/>
+      <c r="B121" s="338"/>
+      <c r="C121" s="338"/>
       <c r="D121" s="30" t="s">
         <v>221</v>
       </c>
@@ -22592,8 +22310,8 @@
     </row>
     <row r="122" spans="1:25" ht="13.2">
       <c r="A122" s="20"/>
-      <c r="B122" s="295"/>
-      <c r="C122" s="296"/>
+      <c r="B122" s="338"/>
+      <c r="C122" s="336"/>
       <c r="D122" s="26" t="s">
         <v>223</v>
       </c>
@@ -22635,8 +22353,8 @@
     </row>
     <row r="123" spans="1:25" ht="21" customHeight="1">
       <c r="A123" s="20"/>
-      <c r="B123" s="295"/>
-      <c r="C123" s="294" t="s">
+      <c r="B123" s="338"/>
+      <c r="C123" s="319" t="s">
         <v>225</v>
       </c>
       <c r="D123" s="41" t="s">
@@ -22684,8 +22402,8 @@
     </row>
     <row r="124" spans="1:25" ht="21" customHeight="1">
       <c r="A124" s="20"/>
-      <c r="B124" s="295"/>
-      <c r="C124" s="296"/>
+      <c r="B124" s="338"/>
+      <c r="C124" s="336"/>
       <c r="D124" s="26" t="s">
         <v>230</v>
       </c>
@@ -22727,8 +22445,8 @@
     </row>
     <row r="125" spans="1:25" ht="13.2">
       <c r="A125" s="20"/>
-      <c r="B125" s="295"/>
-      <c r="C125" s="294" t="s">
+      <c r="B125" s="338"/>
+      <c r="C125" s="319" t="s">
         <v>232</v>
       </c>
       <c r="D125" s="26" t="s">
@@ -22772,8 +22490,8 @@
     </row>
     <row r="126" spans="1:25" ht="13.2">
       <c r="A126" s="20"/>
-      <c r="B126" s="296"/>
-      <c r="C126" s="296"/>
+      <c r="B126" s="336"/>
+      <c r="C126" s="336"/>
       <c r="D126" s="26" t="s">
         <v>235</v>
       </c>
@@ -22814,10 +22532,10 @@
       </c>
     </row>
     <row r="127" spans="1:25" ht="13.2">
-      <c r="A127" s="356" t="s">
+      <c r="A127" s="365" t="s">
         <v>237</v>
       </c>
-      <c r="B127" s="311" t="s">
+      <c r="B127" s="332" t="s">
         <v>238</v>
       </c>
       <c r="C127" s="48" t="s">
@@ -22871,8 +22589,8 @@
       </c>
     </row>
     <row r="128" spans="1:25" ht="26.4">
-      <c r="A128" s="357"/>
-      <c r="B128" s="312"/>
+      <c r="A128" s="366"/>
+      <c r="B128" s="333"/>
       <c r="C128" s="48" t="s">
         <v>239</v>
       </c>
@@ -22924,8 +22642,8 @@
       </c>
     </row>
     <row r="129" spans="1:25" ht="26.4">
-      <c r="A129" s="357"/>
-      <c r="B129" s="312"/>
+      <c r="A129" s="366"/>
+      <c r="B129" s="333"/>
       <c r="C129" s="48" t="s">
         <v>244</v>
       </c>
@@ -22978,8 +22696,8 @@
       </c>
     </row>
     <row r="130" spans="1:25" ht="26.4">
-      <c r="A130" s="357"/>
-      <c r="B130" s="312"/>
+      <c r="A130" s="366"/>
+      <c r="B130" s="333"/>
       <c r="C130" s="48" t="s">
         <v>28</v>
       </c>
@@ -23031,8 +22749,8 @@
       </c>
     </row>
     <row r="131" spans="1:25" ht="39.6">
-      <c r="A131" s="357"/>
-      <c r="B131" s="312"/>
+      <c r="A131" s="366"/>
+      <c r="B131" s="333"/>
       <c r="C131" s="48" t="s">
         <v>26</v>
       </c>
@@ -23084,8 +22802,8 @@
       </c>
     </row>
     <row r="132" spans="1:25" ht="13.2">
-      <c r="A132" s="357"/>
-      <c r="B132" s="353"/>
+      <c r="A132" s="366"/>
+      <c r="B132" s="369"/>
       <c r="C132" s="48" t="s">
         <v>28</v>
       </c>
@@ -23128,10 +22846,10 @@
     </row>
     <row r="133" spans="1:25" ht="13.2">
       <c r="A133" s="20"/>
-      <c r="B133" s="322" t="s">
+      <c r="B133" s="296" t="s">
         <v>254</v>
       </c>
-      <c r="C133" s="321" t="s">
+      <c r="C133" s="305" t="s">
         <v>255</v>
       </c>
       <c r="D133" s="44" t="s">
@@ -23171,8 +22889,8 @@
     </row>
     <row r="134" spans="1:25" ht="25.5" customHeight="1">
       <c r="A134" s="20"/>
-      <c r="B134" s="290"/>
-      <c r="C134" s="350"/>
+      <c r="B134" s="328"/>
+      <c r="C134" s="367"/>
       <c r="D134" s="26" t="s">
         <v>256</v>
       </c>
@@ -23216,8 +22934,8 @@
     </row>
     <row r="135" spans="1:25" ht="13.2">
       <c r="A135" s="20"/>
-      <c r="B135" s="290"/>
-      <c r="C135" s="321" t="s">
+      <c r="B135" s="328"/>
+      <c r="C135" s="305" t="s">
         <v>259</v>
       </c>
       <c r="D135" s="30" t="s">
@@ -23267,8 +22985,8 @@
     </row>
     <row r="136" spans="1:25" ht="13.2">
       <c r="A136" s="20"/>
-      <c r="B136" s="290"/>
-      <c r="C136" s="295"/>
+      <c r="B136" s="328"/>
+      <c r="C136" s="338"/>
       <c r="D136" s="41" t="s">
         <v>263</v>
       </c>
@@ -23310,8 +23028,8 @@
     </row>
     <row r="137" spans="1:25" ht="13.2">
       <c r="A137" s="20"/>
-      <c r="B137" s="290"/>
-      <c r="C137" s="296"/>
+      <c r="B137" s="328"/>
+      <c r="C137" s="336"/>
       <c r="D137" s="26" t="s">
         <v>265</v>
       </c>
@@ -23347,8 +23065,8 @@
     </row>
     <row r="138" spans="1:25" ht="13.2">
       <c r="A138" s="20"/>
-      <c r="B138" s="290"/>
-      <c r="C138" s="321" t="s">
+      <c r="B138" s="328"/>
+      <c r="C138" s="305" t="s">
         <v>270</v>
       </c>
       <c r="D138" s="30" t="s">
@@ -23398,8 +23116,8 @@
     </row>
     <row r="139" spans="1:25" ht="26.4">
       <c r="A139" s="20"/>
-      <c r="B139" s="290"/>
-      <c r="C139" s="295"/>
+      <c r="B139" s="328"/>
+      <c r="C139" s="338"/>
       <c r="D139" s="41" t="s">
         <v>272</v>
       </c>
@@ -23439,8 +23157,8 @@
     </row>
     <row r="140" spans="1:25" ht="13.2">
       <c r="A140" s="20"/>
-      <c r="B140" s="290"/>
-      <c r="C140" s="295"/>
+      <c r="B140" s="328"/>
+      <c r="C140" s="338"/>
       <c r="D140" s="26" t="s">
         <v>273</v>
       </c>
@@ -23480,8 +23198,8 @@
     </row>
     <row r="141" spans="1:25" ht="13.2">
       <c r="A141" s="20"/>
-      <c r="B141" s="290"/>
-      <c r="C141" s="296"/>
+      <c r="B141" s="328"/>
+      <c r="C141" s="336"/>
       <c r="D141" s="26" t="s">
         <v>274</v>
       </c>
@@ -23515,7 +23233,7 @@
     </row>
     <row r="142" spans="1:25" ht="13.2">
       <c r="A142" s="20"/>
-      <c r="B142" s="291"/>
+      <c r="B142" s="297"/>
       <c r="C142" s="27" t="s">
         <v>276</v>
       </c>
@@ -23631,6 +23349,36 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="B133:B142"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="B4:B32"/>
+    <mergeCell ref="B33:B58"/>
+    <mergeCell ref="B59:B83"/>
+    <mergeCell ref="B84:B107"/>
+    <mergeCell ref="B108:B116"/>
+    <mergeCell ref="B117:B126"/>
+    <mergeCell ref="B127:B132"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="C60:C63"/>
+    <mergeCell ref="C64:C67"/>
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="C110:C112"/>
+    <mergeCell ref="A127:A132"/>
+    <mergeCell ref="C9:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="V26:V30"/>
+    <mergeCell ref="U33:U58"/>
+    <mergeCell ref="C54:C58"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="C50:C53"/>
     <mergeCell ref="J1:Q1"/>
     <mergeCell ref="C123:C124"/>
     <mergeCell ref="C125:C126"/>
@@ -23647,36 +23395,6 @@
     <mergeCell ref="C117:C119"/>
     <mergeCell ref="C113:C115"/>
     <mergeCell ref="C5:C8"/>
-    <mergeCell ref="V26:V30"/>
-    <mergeCell ref="U33:U58"/>
-    <mergeCell ref="C54:C58"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="C110:C112"/>
-    <mergeCell ref="A127:A132"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="B133:B142"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="B4:B32"/>
-    <mergeCell ref="B33:B58"/>
-    <mergeCell ref="B59:B83"/>
-    <mergeCell ref="B84:B107"/>
-    <mergeCell ref="B108:B116"/>
-    <mergeCell ref="B117:B126"/>
-    <mergeCell ref="B127:B132"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="C38:C43"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="C60:C63"/>
-    <mergeCell ref="C64:C67"/>
-    <mergeCell ref="C71:C73"/>
   </mergeCells>
   <conditionalFormatting sqref="E1:E1120 Y3:Y144">
     <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="Ja">
@@ -23777,6 +23495,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="03763a1d-3ef6-4dac-84db-711c24c35716">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004E32BC299DDA75418A481CE8C1C04767" ma:contentTypeVersion="10" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="0fa4796f6798a7b079311364fca30a32">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="03763a1d-3ef6-4dac-84db-711c24c35716" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ccd651f340b356ff6f610107a3061652" ns2:_="">
     <xsd:import namespace="03763a1d-3ef6-4dac-84db-711c24c35716"/>
@@ -23954,39 +23691,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="03763a1d-3ef6-4dac-84db-711c24c35716">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{129E9417-0AA3-48C5-9120-B4CEE9FAE9F0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02FC3A6B-F3D8-4BAB-ADCD-470806C7FA83}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="03763a1d-3ef6-4dac-84db-711c24c35716"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -24010,9 +23718,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02FC3A6B-F3D8-4BAB-ADCD-470806C7FA83}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{129E9417-0AA3-48C5-9120-B4CEE9FAE9F0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="03763a1d-3ef6-4dac-84db-711c24c35716"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>